--- a/baocao1.xlsx
+++ b/baocao1.xlsx
@@ -14,103 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="61">
-  <si>
-    <t>2021-10-01</t>
-  </si>
-  <si>
-    <t>2021-10-02</t>
-  </si>
-  <si>
-    <t>2021-10-03</t>
-  </si>
-  <si>
-    <t>2021-10-04</t>
-  </si>
-  <si>
-    <t>2021-10-05</t>
-  </si>
-  <si>
-    <t>2021-10-06</t>
-  </si>
-  <si>
-    <t>2021-10-07</t>
-  </si>
-  <si>
-    <t>2021-10-08</t>
-  </si>
-  <si>
-    <t>2021-10-09</t>
-  </si>
-  <si>
-    <t>2021-10-10</t>
-  </si>
-  <si>
-    <t>2021-10-11</t>
-  </si>
-  <si>
-    <t>2021-10-12</t>
-  </si>
-  <si>
-    <t>2021-10-13</t>
-  </si>
-  <si>
-    <t>2021-10-14</t>
-  </si>
-  <si>
-    <t>2021-10-15</t>
-  </si>
-  <si>
-    <t>2021-10-16</t>
-  </si>
-  <si>
-    <t>2021-10-17</t>
-  </si>
-  <si>
-    <t>2021-10-18</t>
-  </si>
-  <si>
-    <t>2021-10-19</t>
-  </si>
-  <si>
-    <t>2021-10-20</t>
-  </si>
-  <si>
-    <t>2021-10-21</t>
-  </si>
-  <si>
-    <t>2021-10-22</t>
-  </si>
-  <si>
-    <t>2021-10-23</t>
-  </si>
-  <si>
-    <t>2021-10-24</t>
-  </si>
-  <si>
-    <t>2021-10-25</t>
-  </si>
-  <si>
-    <t>2021-10-26</t>
-  </si>
-  <si>
-    <t>2021-10-27</t>
-  </si>
-  <si>
-    <t>2021-10-28</t>
-  </si>
-  <si>
-    <t>2021-10-29</t>
-  </si>
-  <si>
-    <t>2021-10-30</t>
-  </si>
-  <si>
-    <t>2021-10-31</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="18">
   <si>
     <t>A</t>
   </si>
@@ -121,46 +25,13 @@
     <t>C</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>B</t>
   </si>
   <si>
     <t>R</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>A1083</t>
-  </si>
-  <si>
-    <t>RRRRR</t>
   </si>
   <si>
     <t>RR</t>
@@ -528,373 +399,307 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A6:CL29"/>
+  <dimension ref="A6:BP29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="6" spans="1:90">
-      <c r="G6" t="s">
-        <v>0</v>
-      </c>
-      <c r="I6" t="s">
+    <row r="6" spans="1:68">
+      <c r="G6">
+        <v>44470</v>
+      </c>
+      <c r="I6">
+        <v>44471</v>
+      </c>
+      <c r="K6">
+        <v>44472</v>
+      </c>
+      <c r="M6">
+        <v>44473</v>
+      </c>
+      <c r="O6">
+        <v>44474</v>
+      </c>
+      <c r="Q6">
+        <v>44475</v>
+      </c>
+      <c r="S6">
+        <v>44476</v>
+      </c>
+      <c r="U6">
+        <v>44477</v>
+      </c>
+      <c r="W6">
+        <v>44478</v>
+      </c>
+      <c r="Y6">
+        <v>44479</v>
+      </c>
+      <c r="AA6">
+        <v>44480</v>
+      </c>
+      <c r="AC6">
+        <v>44481</v>
+      </c>
+      <c r="AE6">
+        <v>44482</v>
+      </c>
+      <c r="AG6">
+        <v>44483</v>
+      </c>
+      <c r="AI6">
+        <v>44484</v>
+      </c>
+      <c r="AK6">
+        <v>44485</v>
+      </c>
+      <c r="AM6">
+        <v>44486</v>
+      </c>
+      <c r="AO6">
+        <v>44487</v>
+      </c>
+      <c r="AQ6">
+        <v>44488</v>
+      </c>
+      <c r="AS6">
+        <v>44489</v>
+      </c>
+      <c r="AU6">
+        <v>44490</v>
+      </c>
+      <c r="AW6">
+        <v>44491</v>
+      </c>
+      <c r="AY6">
+        <v>44492</v>
+      </c>
+      <c r="BA6">
+        <v>44493</v>
+      </c>
+      <c r="BC6">
+        <v>44494</v>
+      </c>
+      <c r="BE6">
+        <v>44495</v>
+      </c>
+      <c r="BG6">
+        <v>44496</v>
+      </c>
+      <c r="BI6">
+        <v>44497</v>
+      </c>
+      <c r="BK6">
+        <v>44498</v>
+      </c>
+      <c r="BM6">
+        <v>44499</v>
+      </c>
+      <c r="BO6">
+        <v>44500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:68">
+      <c r="A8">
         <v>1</v>
       </c>
-      <c r="K6" t="s">
-        <v>2</v>
-      </c>
-      <c r="M6" t="s">
-        <v>3</v>
-      </c>
-      <c r="O6" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>5</v>
-      </c>
-      <c r="S6" t="s">
-        <v>6</v>
-      </c>
-      <c r="U6" t="s">
-        <v>7</v>
-      </c>
-      <c r="W6" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>11</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>13</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>14</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>16</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>17</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>18</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>20</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>21</v>
-      </c>
-      <c r="AY6" t="s">
-        <v>22</v>
-      </c>
-      <c r="BA6" t="s">
-        <v>23</v>
-      </c>
-      <c r="BC6" t="s">
-        <v>24</v>
-      </c>
-      <c r="BE6" t="s">
-        <v>25</v>
-      </c>
-      <c r="BG6" t="s">
-        <v>26</v>
-      </c>
-      <c r="BI6" t="s">
-        <v>27</v>
-      </c>
-      <c r="BK6" t="s">
-        <v>28</v>
-      </c>
-      <c r="BM6" t="s">
-        <v>29</v>
-      </c>
-      <c r="BO6" t="s">
-        <v>30</v>
-      </c>
-      <c r="BQ6">
+      <c r="G8" t="s">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" t="s">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
         <v>1</v>
-      </c>
-      <c r="BR6">
-        <v>2</v>
-      </c>
-      <c r="BS6">
-        <v>3</v>
-      </c>
-      <c r="BT6">
-        <v>4</v>
-      </c>
-      <c r="BU6">
-        <v>5</v>
-      </c>
-      <c r="BV6">
-        <v>6</v>
-      </c>
-      <c r="BW6">
-        <v>7</v>
-      </c>
-      <c r="BX6">
-        <v>8</v>
-      </c>
-      <c r="BY6">
-        <v>9</v>
-      </c>
-      <c r="BZ6">
-        <v>10</v>
-      </c>
-      <c r="CA6">
-        <v>11</v>
-      </c>
-      <c r="CB6">
-        <v>12</v>
-      </c>
-      <c r="CC6">
-        <v>13</v>
-      </c>
-      <c r="CD6">
-        <v>14</v>
-      </c>
-      <c r="CE6">
-        <v>15</v>
-      </c>
-      <c r="CF6">
-        <v>16</v>
-      </c>
-      <c r="CG6">
-        <v>17</v>
-      </c>
-      <c r="CH6">
-        <v>18</v>
-      </c>
-      <c r="CI6">
-        <v>19</v>
-      </c>
-      <c r="CJ6">
-        <v>20</v>
-      </c>
-      <c r="CK6">
-        <v>21</v>
-      </c>
-      <c r="CL6">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:90">
-      <c r="A8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" t="s">
-        <v>33</v>
       </c>
       <c r="L8">
         <v>7.5</v>
       </c>
       <c r="M8" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="N8">
         <v>4</v>
       </c>
       <c r="O8" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="P8">
         <v>4</v>
       </c>
       <c r="Q8" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="R8">
         <v>4</v>
       </c>
       <c r="S8" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="T8">
         <v>4</v>
       </c>
       <c r="U8" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="V8">
         <v>4</v>
       </c>
       <c r="W8" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="X8">
         <v>4</v>
       </c>
       <c r="Y8" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="Z8">
         <v>11.5</v>
       </c>
       <c r="AA8" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AB8">
         <v>3.8</v>
       </c>
       <c r="AC8" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AD8">
         <v>4</v>
       </c>
       <c r="AE8" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AF8">
         <v>4</v>
       </c>
       <c r="AG8" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AH8">
         <v>4</v>
       </c>
       <c r="AI8" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
         <v>4</v>
       </c>
       <c r="AK8" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AL8">
         <v>4</v>
       </c>
       <c r="AM8" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="AN8">
         <v>12</v>
       </c>
       <c r="AO8" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AP8">
         <v>4</v>
       </c>
       <c r="AQ8" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AR8">
         <v>4</v>
       </c>
       <c r="AS8" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AT8">
         <v>4</v>
       </c>
       <c r="AU8" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AV8">
         <v>4</v>
       </c>
       <c r="AW8" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AX8">
         <v>4</v>
       </c>
       <c r="AY8" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AZ8">
         <v>4</v>
       </c>
       <c r="BA8" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="BB8">
         <v>11.5</v>
       </c>
       <c r="BC8" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BD8">
         <v>3.8</v>
       </c>
       <c r="BE8" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BF8">
         <v>4</v>
       </c>
       <c r="BG8" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BH8">
         <v>4</v>
       </c>
       <c r="BI8" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BJ8">
         <v>4</v>
       </c>
       <c r="BK8" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BL8">
         <v>4</v>
       </c>
       <c r="BM8" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BN8">
         <v>4</v>
       </c>
       <c r="BO8" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="BP8">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:90">
-      <c r="A9" t="s">
-        <v>35</v>
+    <row r="9" spans="1:68">
+      <c r="A9">
+        <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="I9" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -903,37 +708,37 @@
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="N9">
         <v>4</v>
       </c>
       <c r="O9" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="P9">
         <v>4</v>
       </c>
       <c r="Q9" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="R9">
         <v>4</v>
       </c>
       <c r="S9" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="T9">
         <v>4</v>
       </c>
       <c r="U9" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="V9">
         <v>4</v>
       </c>
       <c r="W9" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="X9">
         <v>4</v>
@@ -942,37 +747,37 @@
         <v>0</v>
       </c>
       <c r="AA9" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AB9">
         <v>4</v>
       </c>
       <c r="AC9" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AD9">
         <v>4</v>
       </c>
       <c r="AE9" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AF9">
         <v>4</v>
       </c>
       <c r="AG9" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AH9">
         <v>4</v>
       </c>
       <c r="AI9" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
         <v>4</v>
       </c>
       <c r="AK9" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AL9">
         <v>4</v>
@@ -981,37 +786,37 @@
         <v>0</v>
       </c>
       <c r="AO9" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AP9">
         <v>4</v>
       </c>
       <c r="AQ9" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AR9">
         <v>4</v>
       </c>
       <c r="AS9" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AT9">
         <v>4</v>
       </c>
       <c r="AU9" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AV9">
         <v>4</v>
       </c>
       <c r="AW9" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AX9">
         <v>4</v>
       </c>
       <c r="AY9" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AZ9">
         <v>4</v>
@@ -1020,37 +825,37 @@
         <v>0</v>
       </c>
       <c r="BC9" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BD9">
         <v>4</v>
       </c>
       <c r="BE9" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BF9">
         <v>4</v>
       </c>
       <c r="BG9" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BH9">
         <v>4</v>
       </c>
       <c r="BI9" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BJ9">
         <v>4</v>
       </c>
       <c r="BK9" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BL9">
         <v>4</v>
       </c>
       <c r="BM9" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BN9">
         <v>4</v>
@@ -1059,18 +864,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:90">
-      <c r="A10" t="s">
-        <v>36</v>
+    <row r="10" spans="1:68">
+      <c r="A10">
+        <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="H10">
         <v>4</v>
       </c>
       <c r="I10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -1079,37 +884,37 @@
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="N10">
         <v>4</v>
       </c>
       <c r="O10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="P10">
         <v>3.5</v>
       </c>
       <c r="Q10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="R10">
         <v>2.5</v>
       </c>
       <c r="S10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="T10">
         <v>1.5</v>
       </c>
       <c r="U10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="V10">
         <v>3.3</v>
       </c>
       <c r="W10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="X10">
         <v>0</v>
@@ -1118,37 +923,37 @@
         <v>0</v>
       </c>
       <c r="AA10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="AB10">
         <v>0</v>
       </c>
       <c r="AC10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="AD10">
         <v>0</v>
       </c>
       <c r="AE10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="AF10">
         <v>2</v>
       </c>
       <c r="AG10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="AH10">
         <v>3</v>
       </c>
       <c r="AI10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="AJ10">
         <v>2.8</v>
       </c>
       <c r="AK10" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1157,37 +962,37 @@
         <v>0</v>
       </c>
       <c r="AO10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="AP10">
         <v>0</v>
       </c>
       <c r="AQ10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="AR10">
         <v>0</v>
       </c>
       <c r="AS10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="AT10">
         <v>1.5</v>
       </c>
       <c r="AU10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="AV10">
         <v>2.5</v>
       </c>
       <c r="AW10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="AX10">
         <v>3</v>
       </c>
       <c r="AY10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="AZ10">
         <v>4</v>
@@ -1196,37 +1001,37 @@
         <v>0</v>
       </c>
       <c r="BC10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="BD10">
         <v>4</v>
       </c>
       <c r="BE10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="BF10">
         <v>4</v>
       </c>
       <c r="BG10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="BH10">
         <v>4</v>
       </c>
       <c r="BI10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="BJ10">
         <v>4</v>
       </c>
       <c r="BK10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="BL10">
         <v>4</v>
       </c>
       <c r="BM10" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="BN10">
         <v>4</v>
@@ -1235,782 +1040,782 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:90">
-      <c r="A11" t="s">
-        <v>39</v>
+    <row r="11" spans="1:68">
+      <c r="A11">
+        <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="L11">
         <v>8</v>
       </c>
       <c r="M11" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="N11">
         <v>4</v>
       </c>
       <c r="O11" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="P11">
         <v>4</v>
       </c>
       <c r="Q11" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="R11">
         <v>4</v>
       </c>
       <c r="S11" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="T11">
         <v>4</v>
       </c>
       <c r="U11" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="V11">
         <v>4</v>
       </c>
       <c r="W11" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="X11">
         <v>4</v>
       </c>
       <c r="Y11" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="Z11">
         <v>11.5</v>
       </c>
       <c r="AA11" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AB11">
         <v>3.8</v>
       </c>
       <c r="AC11" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AD11">
         <v>4</v>
       </c>
       <c r="AE11" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AF11">
         <v>4</v>
       </c>
       <c r="AG11" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AH11">
         <v>4</v>
       </c>
       <c r="AI11" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AJ11">
         <v>4</v>
       </c>
       <c r="AK11" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AL11">
         <v>4</v>
       </c>
       <c r="AM11" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="AN11">
         <v>12</v>
       </c>
       <c r="AO11" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AP11">
         <v>4</v>
       </c>
       <c r="AQ11" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AR11">
         <v>4</v>
       </c>
       <c r="AS11" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AT11">
         <v>4</v>
       </c>
       <c r="AU11" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AV11">
         <v>4</v>
       </c>
       <c r="AW11" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AX11">
         <v>4</v>
       </c>
       <c r="AY11" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AZ11">
         <v>4</v>
       </c>
       <c r="BA11" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="BB11">
         <v>11.5</v>
       </c>
       <c r="BC11" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BD11">
         <v>3.8</v>
       </c>
       <c r="BE11" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BF11">
         <v>4</v>
       </c>
       <c r="BG11" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BH11">
         <v>4</v>
       </c>
       <c r="BI11" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BJ11">
         <v>4</v>
       </c>
       <c r="BK11" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BL11">
         <v>4</v>
       </c>
       <c r="BM11" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BN11">
         <v>4</v>
       </c>
       <c r="BO11" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="BP11">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:90">
-      <c r="A12" t="s">
-        <v>40</v>
+    <row r="12" spans="1:68">
+      <c r="A12">
+        <v>3</v>
       </c>
       <c r="G12" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H12">
         <v>0.5</v>
       </c>
       <c r="I12" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J12">
         <v>0.5</v>
       </c>
       <c r="K12" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="L12">
         <v>8.5</v>
       </c>
       <c r="M12" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="N12">
         <v>4</v>
       </c>
       <c r="O12" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="P12">
         <v>4</v>
       </c>
       <c r="Q12" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="R12">
         <v>4</v>
       </c>
       <c r="S12" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="T12">
         <v>4</v>
       </c>
       <c r="U12" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="V12">
         <v>4</v>
       </c>
       <c r="W12" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="X12">
         <v>4</v>
       </c>
       <c r="Y12" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="Z12">
         <v>11.5</v>
       </c>
       <c r="AA12" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AB12">
         <v>3.8</v>
       </c>
       <c r="AC12" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AD12">
         <v>4</v>
       </c>
       <c r="AE12" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AF12">
         <v>4</v>
       </c>
       <c r="AG12" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AH12">
         <v>4</v>
       </c>
       <c r="AI12" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AJ12">
         <v>4</v>
       </c>
       <c r="AK12" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AL12">
         <v>4</v>
       </c>
       <c r="AM12" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="AN12">
         <v>12</v>
       </c>
       <c r="AO12" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AP12">
         <v>4</v>
       </c>
       <c r="AQ12" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AR12">
         <v>4</v>
       </c>
       <c r="AS12" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AT12">
         <v>4</v>
       </c>
       <c r="AU12" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AV12">
         <v>4</v>
       </c>
       <c r="AW12" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AX12">
         <v>4</v>
       </c>
       <c r="AY12" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AZ12">
         <v>4</v>
       </c>
       <c r="BA12" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="BB12">
         <v>11.5</v>
       </c>
       <c r="BC12" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BD12">
         <v>3.8</v>
       </c>
       <c r="BE12" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BF12">
         <v>4</v>
       </c>
       <c r="BG12" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BH12">
         <v>4</v>
       </c>
       <c r="BI12" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BJ12">
         <v>4</v>
       </c>
       <c r="BK12" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BL12">
         <v>4</v>
       </c>
       <c r="BM12" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BN12">
         <v>4</v>
       </c>
       <c r="BO12" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="BP12">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:90">
-      <c r="A13" t="s">
-        <v>41</v>
+    <row r="13" spans="1:68">
+      <c r="A13">
+        <v>4</v>
       </c>
       <c r="G13" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="L13">
         <v>9.5</v>
       </c>
       <c r="M13" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="N13">
         <v>4</v>
       </c>
       <c r="O13" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="P13">
         <v>4</v>
       </c>
       <c r="Q13" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="R13">
         <v>4</v>
       </c>
       <c r="S13" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="T13">
         <v>4</v>
       </c>
       <c r="U13" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="V13">
         <v>4</v>
       </c>
       <c r="W13" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="X13">
         <v>4</v>
       </c>
       <c r="Y13" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="Z13">
         <v>11.5</v>
       </c>
       <c r="AA13" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AB13">
         <v>3.8</v>
       </c>
       <c r="AC13" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AD13">
         <v>4</v>
       </c>
       <c r="AE13" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AF13">
         <v>4</v>
       </c>
       <c r="AG13" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AH13">
         <v>4</v>
       </c>
       <c r="AI13" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AJ13">
         <v>4</v>
       </c>
       <c r="AK13" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AL13">
         <v>4</v>
       </c>
       <c r="AM13" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="AN13">
         <v>12</v>
       </c>
       <c r="AO13" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AP13">
         <v>4</v>
       </c>
       <c r="AQ13" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AR13">
         <v>4</v>
       </c>
       <c r="AS13" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AT13">
         <v>4</v>
       </c>
       <c r="AU13" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AV13">
         <v>4</v>
       </c>
       <c r="AW13" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AX13">
         <v>4</v>
       </c>
       <c r="AY13" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AZ13">
         <v>4</v>
       </c>
       <c r="BA13" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="BB13">
         <v>11.5</v>
       </c>
       <c r="BC13" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BD13">
         <v>3.8</v>
       </c>
       <c r="BE13" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BF13">
         <v>4</v>
       </c>
       <c r="BG13" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BH13">
         <v>4</v>
       </c>
       <c r="BI13" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BJ13">
         <v>4</v>
       </c>
       <c r="BK13" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BL13">
         <v>4</v>
       </c>
       <c r="BM13" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BN13">
         <v>4</v>
       </c>
       <c r="BO13" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="BP13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:90">
-      <c r="A14" t="s">
-        <v>42</v>
+    <row r="14" spans="1:68">
+      <c r="A14">
+        <v>5</v>
       </c>
       <c r="G14" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H14">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="L14">
         <v>10.5</v>
       </c>
       <c r="M14" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="N14">
         <v>4</v>
       </c>
       <c r="O14" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="P14">
         <v>4</v>
       </c>
       <c r="Q14" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="R14">
         <v>4</v>
       </c>
       <c r="S14" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="T14">
         <v>4</v>
       </c>
       <c r="U14" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="V14">
         <v>4</v>
       </c>
       <c r="W14" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="X14">
         <v>4</v>
       </c>
       <c r="Y14" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="Z14">
         <v>11.5</v>
       </c>
       <c r="AA14" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AB14">
         <v>3.8</v>
       </c>
       <c r="AC14" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AD14">
         <v>4</v>
       </c>
       <c r="AE14" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AF14">
         <v>4</v>
       </c>
       <c r="AG14" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AH14">
         <v>4</v>
       </c>
       <c r="AI14" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
         <v>4</v>
       </c>
       <c r="AK14" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AL14">
         <v>4</v>
       </c>
       <c r="AM14" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="AN14">
         <v>12</v>
       </c>
       <c r="AO14" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AP14">
         <v>4</v>
       </c>
       <c r="AQ14" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AR14">
         <v>4</v>
       </c>
       <c r="AS14" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AT14">
         <v>4</v>
       </c>
       <c r="AU14" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AV14">
         <v>4</v>
       </c>
       <c r="AW14" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AX14">
         <v>4</v>
       </c>
       <c r="AY14" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AZ14">
         <v>4</v>
       </c>
       <c r="BA14" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="BB14">
         <v>11.5</v>
       </c>
       <c r="BC14" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BD14">
         <v>3.8</v>
       </c>
       <c r="BE14" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BF14">
         <v>4</v>
       </c>
       <c r="BG14" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BH14">
         <v>4</v>
       </c>
       <c r="BI14" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BJ14">
         <v>4</v>
       </c>
       <c r="BK14" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BL14">
         <v>4</v>
       </c>
       <c r="BM14" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BN14">
         <v>4</v>
       </c>
       <c r="BO14" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="BP14">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:90">
-      <c r="A15" t="s">
-        <v>43</v>
+    <row r="15" spans="1:68">
+      <c r="A15">
+        <v>6</v>
       </c>
       <c r="G15" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H15">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -2019,37 +1824,37 @@
         <v>0</v>
       </c>
       <c r="M15" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="N15">
         <v>4</v>
       </c>
       <c r="O15" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="P15">
         <v>4</v>
       </c>
       <c r="Q15" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="R15">
         <v>4</v>
       </c>
       <c r="S15" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="T15">
         <v>4</v>
       </c>
       <c r="U15" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="V15">
         <v>4</v>
       </c>
       <c r="W15" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="X15">
         <v>4</v>
@@ -2058,37 +1863,37 @@
         <v>0</v>
       </c>
       <c r="AA15" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AB15">
         <v>4</v>
       </c>
       <c r="AC15" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AD15">
         <v>4</v>
       </c>
       <c r="AE15" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AF15">
         <v>4</v>
       </c>
       <c r="AG15" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AH15">
         <v>4</v>
       </c>
       <c r="AI15" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AJ15">
         <v>4</v>
       </c>
       <c r="AK15" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AL15">
         <v>4</v>
@@ -2097,37 +1902,37 @@
         <v>0</v>
       </c>
       <c r="AO15" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AP15">
         <v>4</v>
       </c>
       <c r="AQ15" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AR15">
         <v>4</v>
       </c>
       <c r="AS15" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AT15">
         <v>4</v>
       </c>
       <c r="AU15" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AV15">
         <v>4</v>
       </c>
       <c r="AW15" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AX15">
         <v>4</v>
       </c>
       <c r="AY15" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AZ15">
         <v>4</v>
@@ -2136,37 +1941,37 @@
         <v>0</v>
       </c>
       <c r="BC15" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BD15">
         <v>4</v>
       </c>
       <c r="BE15" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BF15">
         <v>4</v>
       </c>
       <c r="BG15" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BH15">
         <v>4</v>
       </c>
       <c r="BI15" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BJ15">
         <v>4</v>
       </c>
       <c r="BK15" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BL15">
         <v>4</v>
       </c>
       <c r="BM15" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BN15">
         <v>4</v>
@@ -2175,18 +1980,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:90">
-      <c r="A16" t="s">
-        <v>44</v>
+    <row r="16" spans="1:68">
+      <c r="A16">
+        <v>7</v>
       </c>
       <c r="G16" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H16">
         <v>4</v>
       </c>
       <c r="I16" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J16">
         <v>4</v>
@@ -2195,37 +2000,37 @@
         <v>0</v>
       </c>
       <c r="M16" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="N16">
         <v>4</v>
       </c>
       <c r="O16" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="P16">
         <v>4</v>
       </c>
       <c r="Q16" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="R16">
         <v>4</v>
       </c>
       <c r="S16" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="T16">
         <v>4</v>
       </c>
       <c r="U16" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="V16">
         <v>4</v>
       </c>
       <c r="W16" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="X16">
         <v>4</v>
@@ -2234,37 +2039,37 @@
         <v>0</v>
       </c>
       <c r="AA16" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AB16">
         <v>4</v>
       </c>
       <c r="AC16" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AD16">
         <v>4</v>
       </c>
       <c r="AE16" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AF16">
         <v>4</v>
       </c>
       <c r="AG16" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AH16">
         <v>4</v>
       </c>
       <c r="AI16" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
         <v>4</v>
       </c>
       <c r="AK16" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AL16">
         <v>4</v>
@@ -2273,37 +2078,37 @@
         <v>0</v>
       </c>
       <c r="AO16" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AP16">
         <v>4</v>
       </c>
       <c r="AQ16" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AR16">
         <v>4</v>
       </c>
       <c r="AS16" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AT16">
         <v>4</v>
       </c>
       <c r="AU16" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AV16">
         <v>4</v>
       </c>
       <c r="AW16" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AX16">
         <v>4</v>
       </c>
       <c r="AY16" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AZ16">
         <v>4</v>
@@ -2312,37 +2117,37 @@
         <v>0</v>
       </c>
       <c r="BC16" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BD16">
         <v>4</v>
       </c>
       <c r="BE16" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BF16">
         <v>4</v>
       </c>
       <c r="BG16" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BH16">
         <v>4</v>
       </c>
       <c r="BI16" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BJ16">
         <v>4</v>
       </c>
       <c r="BK16" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BL16">
         <v>4</v>
       </c>
       <c r="BM16" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BN16">
         <v>4</v>
@@ -2352,17 +2157,17 @@
       </c>
     </row>
     <row r="17" spans="1:68">
-      <c r="A17" t="s">
-        <v>45</v>
+      <c r="A17">
+        <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H17">
         <v>4</v>
       </c>
       <c r="I17" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J17">
         <v>4</v>
@@ -2371,37 +2176,37 @@
         <v>0</v>
       </c>
       <c r="M17" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="N17">
         <v>4</v>
       </c>
       <c r="O17" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="P17">
         <v>4</v>
       </c>
       <c r="Q17" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="R17">
         <v>4</v>
       </c>
       <c r="S17" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="T17">
         <v>4</v>
       </c>
       <c r="U17" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="V17">
         <v>4</v>
       </c>
       <c r="W17" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="X17">
         <v>4</v>
@@ -2410,37 +2215,37 @@
         <v>0</v>
       </c>
       <c r="AA17" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AB17">
         <v>4</v>
       </c>
       <c r="AC17" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AD17">
         <v>4</v>
       </c>
       <c r="AE17" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AF17">
         <v>4</v>
       </c>
       <c r="AG17" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AH17">
         <v>4</v>
       </c>
       <c r="AI17" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
         <v>4</v>
       </c>
       <c r="AK17" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AL17">
         <v>4</v>
@@ -2449,37 +2254,37 @@
         <v>0</v>
       </c>
       <c r="AO17" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AP17">
         <v>4</v>
       </c>
       <c r="AQ17" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AR17">
         <v>4</v>
       </c>
       <c r="AS17" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AT17">
         <v>4</v>
       </c>
       <c r="AU17" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AV17">
         <v>4</v>
       </c>
       <c r="AW17" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AX17">
         <v>4</v>
       </c>
       <c r="AY17" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AZ17">
         <v>4</v>
@@ -2488,37 +2293,37 @@
         <v>0</v>
       </c>
       <c r="BC17" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BD17">
         <v>4</v>
       </c>
       <c r="BE17" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BF17">
         <v>4</v>
       </c>
       <c r="BG17" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BH17">
         <v>4</v>
       </c>
       <c r="BI17" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BJ17">
         <v>4</v>
       </c>
       <c r="BK17" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BL17">
         <v>4</v>
       </c>
       <c r="BM17" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BN17">
         <v>4</v>
@@ -2528,17 +2333,17 @@
       </c>
     </row>
     <row r="18" spans="1:68">
-      <c r="A18" t="s">
-        <v>46</v>
+      <c r="A18">
+        <v>9</v>
       </c>
       <c r="G18" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H18">
         <v>4</v>
       </c>
       <c r="I18" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J18">
         <v>4</v>
@@ -2547,37 +2352,37 @@
         <v>0</v>
       </c>
       <c r="M18" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="N18">
         <v>4</v>
       </c>
       <c r="O18" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="P18">
         <v>4</v>
       </c>
       <c r="Q18" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="R18">
         <v>4</v>
       </c>
       <c r="S18" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="T18">
         <v>4</v>
       </c>
       <c r="U18" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="V18">
         <v>4</v>
       </c>
       <c r="W18" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="X18">
         <v>4</v>
@@ -2586,37 +2391,37 @@
         <v>0</v>
       </c>
       <c r="AA18" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AB18">
         <v>4</v>
       </c>
       <c r="AC18" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AD18">
         <v>4</v>
       </c>
       <c r="AE18" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AF18">
         <v>4</v>
       </c>
       <c r="AG18" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AH18">
         <v>4</v>
       </c>
       <c r="AI18" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AJ18">
         <v>4</v>
       </c>
       <c r="AK18" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AL18">
         <v>4</v>
@@ -2625,37 +2430,37 @@
         <v>0</v>
       </c>
       <c r="AO18" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AP18">
         <v>4</v>
       </c>
       <c r="AQ18" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AR18">
         <v>4</v>
       </c>
       <c r="AS18" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AT18">
         <v>4</v>
       </c>
       <c r="AU18" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AV18">
         <v>4</v>
       </c>
       <c r="AW18" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AX18">
         <v>4</v>
       </c>
       <c r="AY18" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AZ18">
         <v>4</v>
@@ -2664,37 +2469,37 @@
         <v>0</v>
       </c>
       <c r="BC18" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BD18">
         <v>4</v>
       </c>
       <c r="BE18" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BF18">
         <v>4</v>
       </c>
       <c r="BG18" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BH18">
         <v>4</v>
       </c>
       <c r="BI18" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BJ18">
         <v>4</v>
       </c>
       <c r="BK18" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BL18">
         <v>4</v>
       </c>
       <c r="BM18" t="s">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BN18">
         <v>4</v>
@@ -2705,190 +2510,190 @@
     </row>
     <row r="19" spans="1:68">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="G19" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>0</v>
       </c>
       <c r="O19" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="P19">
         <v>0</v>
       </c>
       <c r="Q19" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="R19">
         <v>0</v>
       </c>
       <c r="S19" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="T19">
         <v>0</v>
       </c>
       <c r="U19" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>0</v>
       </c>
       <c r="W19" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>0</v>
       </c>
       <c r="Y19" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="Z19">
         <v>0</v>
       </c>
       <c r="AA19" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="AB19">
         <v>0</v>
       </c>
       <c r="AC19" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="AD19">
         <v>0</v>
       </c>
       <c r="AE19" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="AF19">
         <v>0</v>
       </c>
       <c r="AG19" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AI19" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="AJ19">
         <v>0</v>
       </c>
       <c r="AK19" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="AN19">
         <v>0</v>
       </c>
       <c r="AO19" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="AP19">
         <v>0</v>
       </c>
       <c r="AQ19" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="AR19">
         <v>0</v>
       </c>
       <c r="AS19" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="AT19">
         <v>0</v>
       </c>
       <c r="AU19" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="AV19">
         <v>0</v>
       </c>
       <c r="AW19" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="AX19">
         <v>0</v>
       </c>
       <c r="AY19" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="AZ19">
         <v>0</v>
       </c>
       <c r="BA19" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="BB19">
         <v>0</v>
       </c>
       <c r="BC19" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="BD19">
         <v>0</v>
       </c>
       <c r="BE19" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="BF19">
         <v>0</v>
       </c>
       <c r="BG19" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="BH19">
         <v>0</v>
       </c>
       <c r="BI19" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="BJ19">
         <v>0</v>
       </c>
       <c r="BK19" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="BL19">
         <v>0</v>
       </c>
       <c r="BM19" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="BN19">
         <v>0</v>
       </c>
       <c r="BO19" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="BP19">
         <v>0</v>
@@ -2896,190 +2701,190 @@
     </row>
     <row r="20" spans="1:68">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="G20" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="N20">
         <v>0</v>
       </c>
       <c r="O20" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>0</v>
       </c>
       <c r="Q20" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="R20">
         <v>0</v>
       </c>
       <c r="S20" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="T20">
         <v>0</v>
       </c>
       <c r="U20" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>0</v>
       </c>
       <c r="W20" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>0</v>
       </c>
       <c r="Y20" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="Z20">
         <v>0</v>
       </c>
       <c r="AA20" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AB20">
         <v>0</v>
       </c>
       <c r="AC20" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AD20">
         <v>0</v>
       </c>
       <c r="AE20" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AF20">
         <v>0</v>
       </c>
       <c r="AG20" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AI20" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AJ20">
         <v>0</v>
       </c>
       <c r="AK20" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="AN20">
         <v>0</v>
       </c>
       <c r="AO20" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AP20">
         <v>0</v>
       </c>
       <c r="AQ20" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AR20">
         <v>0</v>
       </c>
       <c r="AS20" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AT20">
         <v>0</v>
       </c>
       <c r="AU20" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AV20">
         <v>0</v>
       </c>
       <c r="AW20" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AX20">
         <v>0</v>
       </c>
       <c r="AY20" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="AZ20">
         <v>0</v>
       </c>
       <c r="BA20" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="BB20">
         <v>0</v>
       </c>
       <c r="BC20" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BD20">
         <v>0</v>
       </c>
       <c r="BE20" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BF20">
         <v>0</v>
       </c>
       <c r="BG20" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BH20">
         <v>0</v>
       </c>
       <c r="BI20" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BJ20">
         <v>0</v>
       </c>
       <c r="BK20" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BL20">
         <v>0</v>
       </c>
       <c r="BM20" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BN20">
         <v>0</v>
       </c>
       <c r="BO20" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="BP20">
         <v>0</v>
@@ -3087,190 +2892,190 @@
     </row>
     <row r="21" spans="1:68">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="G21" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>0</v>
       </c>
       <c r="O21" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="P21">
         <v>0</v>
       </c>
       <c r="Q21" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="R21">
         <v>0</v>
       </c>
       <c r="S21" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>0</v>
       </c>
       <c r="U21" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>0</v>
       </c>
       <c r="W21" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>0</v>
       </c>
       <c r="Y21" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="Z21">
         <v>0</v>
       </c>
       <c r="AA21" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AB21">
         <v>0</v>
       </c>
       <c r="AC21" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AD21">
         <v>0</v>
       </c>
       <c r="AE21" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AF21">
         <v>0</v>
       </c>
       <c r="AG21" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AI21" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AJ21">
         <v>0</v>
       </c>
       <c r="AK21" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="AN21">
         <v>0</v>
       </c>
       <c r="AO21" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AP21">
         <v>0</v>
       </c>
       <c r="AQ21" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AR21">
         <v>0</v>
       </c>
       <c r="AS21" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AT21">
         <v>0</v>
       </c>
       <c r="AU21" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AV21">
         <v>0</v>
       </c>
       <c r="AW21" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AX21">
         <v>0</v>
       </c>
       <c r="AY21" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="AZ21">
         <v>0</v>
       </c>
       <c r="BA21" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="BB21">
         <v>0</v>
       </c>
       <c r="BC21" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BD21">
         <v>0</v>
       </c>
       <c r="BE21" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BF21">
         <v>0</v>
       </c>
       <c r="BG21" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BH21">
         <v>0</v>
       </c>
       <c r="BI21" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BJ21">
         <v>0</v>
       </c>
       <c r="BK21" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BL21">
         <v>0</v>
       </c>
       <c r="BM21" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BN21">
         <v>0</v>
       </c>
       <c r="BO21" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="BP21">
         <v>0</v>
@@ -3278,190 +3083,190 @@
     </row>
     <row r="22" spans="1:68">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="G22" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="P22">
         <v>0</v>
       </c>
       <c r="Q22" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="R22">
         <v>0</v>
       </c>
       <c r="S22" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>0</v>
       </c>
       <c r="U22" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>0</v>
       </c>
       <c r="W22" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>0</v>
       </c>
       <c r="Y22" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="Z22">
         <v>0</v>
       </c>
       <c r="AA22" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AB22">
         <v>0</v>
       </c>
       <c r="AC22" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AD22">
         <v>0</v>
       </c>
       <c r="AE22" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AF22">
         <v>0</v>
       </c>
       <c r="AG22" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AI22" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AJ22">
         <v>0</v>
       </c>
       <c r="AK22" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AL22">
         <v>0</v>
       </c>
       <c r="AM22" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="AN22">
         <v>0</v>
       </c>
       <c r="AO22" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AP22">
         <v>0</v>
       </c>
       <c r="AQ22" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AR22">
         <v>0</v>
       </c>
       <c r="AS22" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AT22">
         <v>0</v>
       </c>
       <c r="AU22" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AV22">
         <v>0</v>
       </c>
       <c r="AW22" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AX22">
         <v>0</v>
       </c>
       <c r="AY22" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="AZ22">
         <v>0</v>
       </c>
       <c r="BA22" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="BB22">
         <v>0</v>
       </c>
       <c r="BC22" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BD22">
         <v>0</v>
       </c>
       <c r="BE22" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BF22">
         <v>0</v>
       </c>
       <c r="BG22" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BH22">
         <v>0</v>
       </c>
       <c r="BI22" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BJ22">
         <v>0</v>
       </c>
       <c r="BK22" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BL22">
         <v>0</v>
       </c>
       <c r="BM22" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BN22">
         <v>0</v>
       </c>
       <c r="BO22" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="BP22">
         <v>0</v>
@@ -3469,190 +3274,190 @@
     </row>
     <row r="23" spans="1:68">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="G23" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>0</v>
       </c>
       <c r="O23" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="P23">
         <v>0</v>
       </c>
       <c r="Q23" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>0</v>
       </c>
       <c r="S23" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>0</v>
       </c>
       <c r="U23" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="V23">
         <v>0</v>
       </c>
       <c r="W23" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>0</v>
       </c>
       <c r="Y23" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="Z23">
         <v>0</v>
       </c>
       <c r="AA23" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>0</v>
       </c>
       <c r="AC23" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AD23">
         <v>0</v>
       </c>
       <c r="AE23" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AF23">
         <v>0</v>
       </c>
       <c r="AG23" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AI23" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AJ23">
         <v>0</v>
       </c>
       <c r="AK23" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AL23">
         <v>0</v>
       </c>
       <c r="AM23" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="AN23">
         <v>0</v>
       </c>
       <c r="AO23" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AP23">
         <v>0</v>
       </c>
       <c r="AQ23" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AR23">
         <v>0</v>
       </c>
       <c r="AS23" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AT23">
         <v>0</v>
       </c>
       <c r="AU23" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AV23">
         <v>0</v>
       </c>
       <c r="AW23" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AX23">
         <v>0</v>
       </c>
       <c r="AY23" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="AZ23">
         <v>0</v>
       </c>
       <c r="BA23" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="BB23">
         <v>0</v>
       </c>
       <c r="BC23" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BD23">
         <v>0</v>
       </c>
       <c r="BE23" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BF23">
         <v>0</v>
       </c>
       <c r="BG23" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BH23">
         <v>0</v>
       </c>
       <c r="BI23" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BJ23">
         <v>0</v>
       </c>
       <c r="BK23" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BL23">
         <v>0</v>
       </c>
       <c r="BM23" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BN23">
         <v>0</v>
       </c>
       <c r="BO23" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="BP23">
         <v>0</v>
@@ -3660,190 +3465,190 @@
     </row>
     <row r="24" spans="1:68">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="G24" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>0</v>
       </c>
       <c r="O24" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="P24">
         <v>0</v>
       </c>
       <c r="Q24" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="R24">
         <v>0</v>
       </c>
       <c r="S24" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>0</v>
       </c>
       <c r="U24" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="V24">
         <v>0</v>
       </c>
       <c r="W24" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="X24">
         <v>0</v>
       </c>
       <c r="Y24" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="Z24">
         <v>0</v>
       </c>
       <c r="AA24" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AB24">
         <v>0</v>
       </c>
       <c r="AC24" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AD24">
         <v>0</v>
       </c>
       <c r="AE24" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AF24">
         <v>0</v>
       </c>
       <c r="AG24" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AI24" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AJ24">
         <v>0</v>
       </c>
       <c r="AK24" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="AN24">
         <v>0</v>
       </c>
       <c r="AO24" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AP24">
         <v>0</v>
       </c>
       <c r="AQ24" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AR24">
         <v>0</v>
       </c>
       <c r="AS24" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AT24">
         <v>0</v>
       </c>
       <c r="AU24" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AV24">
         <v>0</v>
       </c>
       <c r="AW24" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AX24">
         <v>0</v>
       </c>
       <c r="AY24" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="AZ24">
         <v>0</v>
       </c>
       <c r="BA24" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="BB24">
         <v>0</v>
       </c>
       <c r="BC24" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BD24">
         <v>0</v>
       </c>
       <c r="BE24" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BF24">
         <v>0</v>
       </c>
       <c r="BG24" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BH24">
         <v>0</v>
       </c>
       <c r="BI24" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BJ24">
         <v>0</v>
       </c>
       <c r="BK24" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BL24">
         <v>0</v>
       </c>
       <c r="BM24" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BN24">
         <v>0</v>
       </c>
       <c r="BO24" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="BP24">
         <v>0</v>
@@ -3851,190 +3656,190 @@
     </row>
     <row r="25" spans="1:68">
       <c r="A25" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="H25">
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="N25">
         <v>0</v>
       </c>
       <c r="O25" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="P25">
         <v>0</v>
       </c>
       <c r="Q25" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="R25">
         <v>0</v>
       </c>
       <c r="S25" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>0</v>
       </c>
       <c r="U25" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="V25">
         <v>0</v>
       </c>
       <c r="W25" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>0</v>
       </c>
       <c r="Y25" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="Z25">
         <v>0</v>
       </c>
       <c r="AA25" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AB25">
         <v>0</v>
       </c>
       <c r="AC25" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AD25">
         <v>0</v>
       </c>
       <c r="AE25" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AF25">
         <v>0</v>
       </c>
       <c r="AG25" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AH25">
         <v>0</v>
       </c>
       <c r="AI25" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AJ25">
         <v>0</v>
       </c>
       <c r="AK25" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="AN25">
         <v>0</v>
       </c>
       <c r="AO25" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AP25">
         <v>0</v>
       </c>
       <c r="AQ25" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AR25">
         <v>0</v>
       </c>
       <c r="AS25" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AT25">
         <v>0</v>
       </c>
       <c r="AU25" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AV25">
         <v>0</v>
       </c>
       <c r="AW25" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AX25">
         <v>0</v>
       </c>
       <c r="AY25" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="AZ25">
         <v>0</v>
       </c>
       <c r="BA25" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="BB25">
         <v>0</v>
       </c>
       <c r="BC25" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BD25">
         <v>0</v>
       </c>
       <c r="BE25" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BF25">
         <v>0</v>
       </c>
       <c r="BG25" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BH25">
         <v>0</v>
       </c>
       <c r="BI25" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BJ25">
         <v>0</v>
       </c>
       <c r="BK25" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BL25">
         <v>0</v>
       </c>
       <c r="BM25" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="BN25">
         <v>0</v>
       </c>
       <c r="BO25" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="BP25">
         <v>0</v>
@@ -4042,190 +3847,190 @@
     </row>
     <row r="26" spans="1:68">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="H26">
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="L26">
         <v>0</v>
       </c>
       <c r="M26" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>0</v>
       </c>
       <c r="O26" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>0</v>
       </c>
       <c r="Q26" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="R26">
         <v>0</v>
       </c>
       <c r="S26" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="T26">
         <v>0</v>
       </c>
       <c r="U26" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>0</v>
       </c>
       <c r="W26" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>0</v>
       </c>
       <c r="Y26" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="Z26">
         <v>0</v>
       </c>
       <c r="AA26" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AB26">
         <v>0</v>
       </c>
       <c r="AC26" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AD26">
         <v>0</v>
       </c>
       <c r="AE26" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AF26">
         <v>0</v>
       </c>
       <c r="AG26" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AI26" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AJ26">
         <v>0</v>
       </c>
       <c r="AK26" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AL26">
         <v>0</v>
       </c>
       <c r="AM26" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="AN26">
         <v>0</v>
       </c>
       <c r="AO26" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AP26">
         <v>0</v>
       </c>
       <c r="AQ26" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AR26">
         <v>0</v>
       </c>
       <c r="AS26" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AT26">
         <v>0</v>
       </c>
       <c r="AU26" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AV26">
         <v>0</v>
       </c>
       <c r="AW26" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AX26">
         <v>0</v>
       </c>
       <c r="AY26" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="AZ26">
         <v>0</v>
       </c>
       <c r="BA26" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="BB26">
         <v>0</v>
       </c>
       <c r="BC26" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BD26">
         <v>0</v>
       </c>
       <c r="BE26" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BF26">
         <v>0</v>
       </c>
       <c r="BG26" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BH26">
         <v>0</v>
       </c>
       <c r="BI26" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BJ26">
         <v>0</v>
       </c>
       <c r="BK26" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BL26">
         <v>0</v>
       </c>
       <c r="BM26" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BN26">
         <v>0</v>
       </c>
       <c r="BO26" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="BP26">
         <v>0</v>
@@ -4233,190 +4038,190 @@
     </row>
     <row r="27" spans="1:68">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="H27">
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>0</v>
       </c>
       <c r="O27" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="P27">
         <v>0</v>
       </c>
       <c r="Q27" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="R27">
         <v>0</v>
       </c>
       <c r="S27" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>0</v>
       </c>
       <c r="U27" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>0</v>
       </c>
       <c r="W27" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>0</v>
       </c>
       <c r="Y27" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="Z27">
         <v>0</v>
       </c>
       <c r="AA27" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AB27">
         <v>0</v>
       </c>
       <c r="AC27" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AD27">
         <v>0</v>
       </c>
       <c r="AE27" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AF27">
         <v>0</v>
       </c>
       <c r="AG27" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AI27" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AJ27">
         <v>0</v>
       </c>
       <c r="AK27" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AL27">
         <v>0</v>
       </c>
       <c r="AM27" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="AN27">
         <v>0</v>
       </c>
       <c r="AO27" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AP27">
         <v>0</v>
       </c>
       <c r="AQ27" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AR27">
         <v>0</v>
       </c>
       <c r="AS27" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AT27">
         <v>0</v>
       </c>
       <c r="AU27" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AV27">
         <v>0</v>
       </c>
       <c r="AW27" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AX27">
         <v>0</v>
       </c>
       <c r="AY27" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="AZ27">
         <v>0</v>
       </c>
       <c r="BA27" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="BB27">
         <v>0</v>
       </c>
       <c r="BC27" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BD27">
         <v>0</v>
       </c>
       <c r="BE27" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BF27">
         <v>0</v>
       </c>
       <c r="BG27" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BH27">
         <v>0</v>
       </c>
       <c r="BI27" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BJ27">
         <v>0</v>
       </c>
       <c r="BK27" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BL27">
         <v>0</v>
       </c>
       <c r="BM27" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BN27">
         <v>0</v>
       </c>
       <c r="BO27" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="BP27">
         <v>0</v>
@@ -4424,190 +4229,190 @@
     </row>
     <row r="28" spans="1:68">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="G28" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="H28">
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="L28">
         <v>0</v>
       </c>
       <c r="M28" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>0</v>
       </c>
       <c r="O28" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="P28">
         <v>0</v>
       </c>
       <c r="Q28" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="R28">
         <v>0</v>
       </c>
       <c r="S28" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>0</v>
       </c>
       <c r="U28" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>0</v>
       </c>
       <c r="W28" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>0</v>
       </c>
       <c r="Y28" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="Z28">
         <v>0</v>
       </c>
       <c r="AA28" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AB28">
         <v>0</v>
       </c>
       <c r="AC28" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AD28">
         <v>0</v>
       </c>
       <c r="AE28" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AF28">
         <v>0</v>
       </c>
       <c r="AG28" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AI28" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AJ28">
         <v>0</v>
       </c>
       <c r="AK28" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AL28">
         <v>0</v>
       </c>
       <c r="AM28" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="AN28">
         <v>0</v>
       </c>
       <c r="AO28" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AP28">
         <v>0</v>
       </c>
       <c r="AQ28" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AR28">
         <v>0</v>
       </c>
       <c r="AS28" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AT28">
         <v>0</v>
       </c>
       <c r="AU28" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AV28">
         <v>0</v>
       </c>
       <c r="AW28" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AX28">
         <v>0</v>
       </c>
       <c r="AY28" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="AZ28">
         <v>0</v>
       </c>
       <c r="BA28" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="BB28">
         <v>0</v>
       </c>
       <c r="BC28" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BD28">
         <v>0</v>
       </c>
       <c r="BE28" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BF28">
         <v>0</v>
       </c>
       <c r="BG28" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BH28">
         <v>0</v>
       </c>
       <c r="BI28" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BJ28">
         <v>0</v>
       </c>
       <c r="BK28" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BL28">
         <v>0</v>
       </c>
       <c r="BM28" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BN28">
         <v>0</v>
       </c>
       <c r="BO28" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="BP28">
         <v>0</v>
@@ -4615,184 +4420,184 @@
     </row>
     <row r="29" spans="1:68">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="G29" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="H29">
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="N29">
         <v>0</v>
       </c>
       <c r="O29" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="P29">
         <v>0</v>
       </c>
       <c r="Q29" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="R29">
         <v>0</v>
       </c>
       <c r="S29" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>0</v>
       </c>
       <c r="U29" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="V29">
         <v>0</v>
       </c>
       <c r="W29" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>0</v>
       </c>
       <c r="Y29" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="Z29">
         <v>0</v>
       </c>
       <c r="AA29" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AB29">
         <v>0</v>
       </c>
       <c r="AC29" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AD29">
         <v>0</v>
       </c>
       <c r="AE29" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AF29">
         <v>0</v>
       </c>
       <c r="AG29" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AH29">
         <v>0</v>
       </c>
       <c r="AI29" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AJ29">
         <v>0</v>
       </c>
       <c r="AK29" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AL29">
         <v>0</v>
       </c>
       <c r="AM29" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="AN29">
         <v>0</v>
       </c>
       <c r="AO29" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AP29">
         <v>0</v>
       </c>
       <c r="AQ29" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AR29">
         <v>0</v>
       </c>
       <c r="AS29" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AT29">
         <v>0</v>
       </c>
       <c r="AU29" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AV29">
         <v>0</v>
       </c>
       <c r="AW29" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AX29">
         <v>0</v>
       </c>
       <c r="AY29" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="AZ29">
         <v>0</v>
       </c>
       <c r="BA29" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="BB29">
         <v>0</v>
       </c>
       <c r="BC29" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BD29">
         <v>0</v>
       </c>
       <c r="BE29" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BF29">
         <v>0</v>
       </c>
       <c r="BG29" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BH29">
         <v>0</v>
       </c>
       <c r="BI29" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BJ29">
         <v>0</v>
       </c>
       <c r="BK29" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BL29">
         <v>0</v>
       </c>
       <c r="BM29" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="BN29">
         <v>0</v>

--- a/baocao1.xlsx
+++ b/baocao1.xlsx
@@ -14,7 +14,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="47">
+  <si>
+    <t>Nhân viên 1</t>
+  </si>
+  <si>
+    <t>San xuat</t>
+  </si>
+  <si>
+    <t>Thứ sáu</t>
+  </si>
+  <si>
+    <t>San xuat sang</t>
+  </si>
   <si>
     <t>A</t>
   </si>
@@ -25,13 +37,55 @@
     <t>C</t>
   </si>
   <si>
+    <t>Nhân viên 10</t>
+  </si>
+  <si>
+    <t>Nhan vien Ca C</t>
+  </si>
+  <si>
+    <t>San xuat Ca C</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
     <t>R</t>
   </si>
   <si>
+    <t>Nhân viên 2</t>
+  </si>
+  <si>
+    <t>Nhân viên 3</t>
+  </si>
+  <si>
+    <t>Nhân viên 4</t>
+  </si>
+  <si>
+    <t>Nhân viên 5</t>
+  </si>
+  <si>
+    <t>Nhân viên 6</t>
+  </si>
+  <si>
+    <t>Nhân viên 7</t>
+  </si>
+  <si>
+    <t>Nhân viên 8</t>
+  </si>
+  <si>
+    <t>Nhân viên 9</t>
+  </si>
+  <si>
     <t>A1083</t>
+  </si>
+  <si>
+    <t>Nguyễn Thuỳ Linh</t>
+  </si>
+  <si>
+    <t>Hanh Chinh Nhan Su</t>
+  </si>
+  <si>
+    <t>Ca Hanh Chính</t>
   </si>
   <si>
     <t>RR</t>
@@ -40,34 +94,67 @@
     <t>A1144</t>
   </si>
   <si>
+    <t>Nguyễn Thị Thanh Thảo</t>
+  </si>
+  <si>
     <t>D</t>
   </si>
   <si>
     <t>A1148</t>
   </si>
   <si>
+    <t>Ngô Thanh Thuỷ</t>
+  </si>
+  <si>
+    <t>QMS</t>
+  </si>
+  <si>
     <t>A1637</t>
+  </si>
+  <si>
+    <t>Trương Mỹ Phụng</t>
   </si>
   <si>
     <t>A1675</t>
   </si>
   <si>
+    <t>Võ Thị Ngọc Dung</t>
+  </si>
+  <si>
     <t>A1795</t>
+  </si>
+  <si>
+    <t>Ngô Thị Hiền</t>
   </si>
   <si>
     <t>A1888</t>
   </si>
   <si>
+    <t>Bùi Văn Dỉnh</t>
+  </si>
+  <si>
     <t>A2065</t>
+  </si>
+  <si>
+    <t>Triệu Quang Ngọc</t>
   </si>
   <si>
     <t>A2071</t>
   </si>
   <si>
+    <t>Nguyễn Chí Tâm</t>
+  </si>
+  <si>
     <t>A2078</t>
   </si>
   <si>
+    <t>Thái Thị Hải Yến</t>
+  </si>
+  <si>
     <t>A800</t>
+  </si>
+  <si>
+    <t>Trần Hoàng Thắng</t>
   </si>
 </sst>
 </file>
@@ -501,188 +588,203 @@
       <c r="A8">
         <v>1</v>
       </c>
+      <c r="B8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>44470</v>
+      </c>
+      <c r="E8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" t="s">
+        <v>3</v>
+      </c>
       <c r="G8" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <v>7.5</v>
       </c>
       <c r="M8" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>4</v>
       </c>
       <c r="O8" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>4</v>
       </c>
       <c r="Q8" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R8">
         <v>4</v>
       </c>
       <c r="S8" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T8">
         <v>4</v>
       </c>
       <c r="U8" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V8">
         <v>4</v>
       </c>
       <c r="W8" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>4</v>
       </c>
       <c r="Y8" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z8">
         <v>11.5</v>
       </c>
       <c r="AA8" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB8">
         <v>3.8</v>
       </c>
       <c r="AC8" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD8">
         <v>4</v>
       </c>
       <c r="AE8" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF8">
         <v>4</v>
       </c>
       <c r="AG8" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH8">
         <v>4</v>
       </c>
       <c r="AI8" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ8">
         <v>4</v>
       </c>
       <c r="AK8" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL8">
         <v>4</v>
       </c>
       <c r="AM8" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AN8">
         <v>12</v>
       </c>
       <c r="AO8" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AP8">
         <v>4</v>
       </c>
       <c r="AQ8" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AR8">
         <v>4</v>
       </c>
       <c r="AS8" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AT8">
         <v>4</v>
       </c>
       <c r="AU8" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV8">
         <v>4</v>
       </c>
       <c r="AW8" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AX8">
         <v>4</v>
       </c>
       <c r="AY8" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AZ8">
         <v>4</v>
       </c>
       <c r="BA8" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BB8">
         <v>11.5</v>
       </c>
       <c r="BC8" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BD8">
         <v>3.8</v>
       </c>
       <c r="BE8" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF8">
         <v>4</v>
       </c>
       <c r="BG8" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH8">
         <v>4</v>
       </c>
       <c r="BI8" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BJ8">
         <v>4</v>
       </c>
       <c r="BK8" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BL8">
         <v>4</v>
       </c>
       <c r="BM8" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BN8">
         <v>4</v>
       </c>
       <c r="BO8" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BP8">
         <v>12</v>
@@ -692,14 +794,29 @@
       <c r="A9">
         <v>10</v>
       </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>44470</v>
+      </c>
+      <c r="E9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>3</v>
+      </c>
       <c r="G9" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9">
         <v>4</v>
       </c>
       <c r="I9" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -708,37 +825,37 @@
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>4</v>
       </c>
       <c r="O9" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>4</v>
       </c>
       <c r="Q9" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R9">
         <v>4</v>
       </c>
       <c r="S9" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T9">
         <v>4</v>
       </c>
       <c r="U9" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>4</v>
       </c>
       <c r="W9" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>4</v>
@@ -747,37 +864,37 @@
         <v>0</v>
       </c>
       <c r="AA9" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB9">
         <v>4</v>
       </c>
       <c r="AC9" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD9">
         <v>4</v>
       </c>
       <c r="AE9" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF9">
         <v>4</v>
       </c>
       <c r="AG9" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH9">
         <v>4</v>
       </c>
       <c r="AI9" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ9">
         <v>4</v>
       </c>
       <c r="AK9" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL9">
         <v>4</v>
@@ -786,37 +903,37 @@
         <v>0</v>
       </c>
       <c r="AO9" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AP9">
         <v>4</v>
       </c>
       <c r="AQ9" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AR9">
         <v>4</v>
       </c>
       <c r="AS9" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AT9">
         <v>4</v>
       </c>
       <c r="AU9" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV9">
         <v>4</v>
       </c>
       <c r="AW9" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AX9">
         <v>4</v>
       </c>
       <c r="AY9" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AZ9">
         <v>4</v>
@@ -825,37 +942,37 @@
         <v>0</v>
       </c>
       <c r="BC9" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BD9">
         <v>4</v>
       </c>
       <c r="BE9" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF9">
         <v>4</v>
       </c>
       <c r="BG9" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH9">
         <v>4</v>
       </c>
       <c r="BI9" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BJ9">
         <v>4</v>
       </c>
       <c r="BK9" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BL9">
         <v>4</v>
       </c>
       <c r="BM9" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BN9">
         <v>4</v>
@@ -868,14 +985,29 @@
       <c r="A10">
         <v>11</v>
       </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>44470</v>
+      </c>
+      <c r="E10" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
       <c r="G10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H10">
         <v>4</v>
       </c>
       <c r="I10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -884,37 +1016,37 @@
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>4</v>
       </c>
       <c r="O10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>3.5</v>
       </c>
       <c r="Q10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>2.5</v>
       </c>
       <c r="S10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>1.5</v>
       </c>
       <c r="U10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V10">
         <v>3.3</v>
       </c>
       <c r="W10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="X10">
         <v>0</v>
@@ -923,37 +1055,37 @@
         <v>0</v>
       </c>
       <c r="AA10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AB10">
         <v>0</v>
       </c>
       <c r="AC10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AD10">
         <v>0</v>
       </c>
       <c r="AE10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AF10">
         <v>2</v>
       </c>
       <c r="AG10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AH10">
         <v>3</v>
       </c>
       <c r="AI10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AJ10">
         <v>2.8</v>
       </c>
       <c r="AK10" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -962,37 +1094,37 @@
         <v>0</v>
       </c>
       <c r="AO10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AP10">
         <v>0</v>
       </c>
       <c r="AQ10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AR10">
         <v>0</v>
       </c>
       <c r="AS10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AT10">
         <v>1.5</v>
       </c>
       <c r="AU10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AV10">
         <v>2.5</v>
       </c>
       <c r="AW10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AX10">
         <v>3</v>
       </c>
       <c r="AY10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AZ10">
         <v>4</v>
@@ -1001,37 +1133,37 @@
         <v>0</v>
       </c>
       <c r="BC10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="BD10">
         <v>4</v>
       </c>
       <c r="BE10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="BF10">
         <v>4</v>
       </c>
       <c r="BG10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="BH10">
         <v>4</v>
       </c>
       <c r="BI10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="BJ10">
         <v>4</v>
       </c>
       <c r="BK10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="BL10">
         <v>4</v>
       </c>
       <c r="BM10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="BN10">
         <v>4</v>
@@ -1044,188 +1176,203 @@
       <c r="A11">
         <v>2</v>
       </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>44470</v>
+      </c>
+      <c r="E11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" t="s">
+        <v>3</v>
+      </c>
       <c r="G11" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>8</v>
       </c>
       <c r="M11" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>4</v>
       </c>
       <c r="O11" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P11">
         <v>4</v>
       </c>
       <c r="Q11" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R11">
         <v>4</v>
       </c>
       <c r="S11" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T11">
         <v>4</v>
       </c>
       <c r="U11" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>4</v>
       </c>
       <c r="W11" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X11">
         <v>4</v>
       </c>
       <c r="Y11" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z11">
         <v>11.5</v>
       </c>
       <c r="AA11" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB11">
         <v>3.8</v>
       </c>
       <c r="AC11" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD11">
         <v>4</v>
       </c>
       <c r="AE11" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF11">
         <v>4</v>
       </c>
       <c r="AG11" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH11">
         <v>4</v>
       </c>
       <c r="AI11" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ11">
         <v>4</v>
       </c>
       <c r="AK11" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL11">
         <v>4</v>
       </c>
       <c r="AM11" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AN11">
         <v>12</v>
       </c>
       <c r="AO11" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AP11">
         <v>4</v>
       </c>
       <c r="AQ11" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AR11">
         <v>4</v>
       </c>
       <c r="AS11" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AT11">
         <v>4</v>
       </c>
       <c r="AU11" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV11">
         <v>4</v>
       </c>
       <c r="AW11" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AX11">
         <v>4</v>
       </c>
       <c r="AY11" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AZ11">
         <v>4</v>
       </c>
       <c r="BA11" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BB11">
         <v>11.5</v>
       </c>
       <c r="BC11" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BD11">
         <v>3.8</v>
       </c>
       <c r="BE11" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF11">
         <v>4</v>
       </c>
       <c r="BG11" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH11">
         <v>4</v>
       </c>
       <c r="BI11" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BJ11">
         <v>4</v>
       </c>
       <c r="BK11" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BL11">
         <v>4</v>
       </c>
       <c r="BM11" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BN11">
         <v>4</v>
       </c>
       <c r="BO11" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BP11">
         <v>12</v>
@@ -1235,188 +1382,203 @@
       <c r="A12">
         <v>3</v>
       </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>44470</v>
+      </c>
+      <c r="E12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" t="s">
+        <v>3</v>
+      </c>
       <c r="G12" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H12">
         <v>0.5</v>
       </c>
       <c r="I12" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J12">
         <v>0.5</v>
       </c>
       <c r="K12" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>8.5</v>
       </c>
       <c r="M12" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>4</v>
       </c>
       <c r="O12" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>4</v>
       </c>
       <c r="Q12" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R12">
         <v>4</v>
       </c>
       <c r="S12" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T12">
         <v>4</v>
       </c>
       <c r="U12" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>4</v>
       </c>
       <c r="W12" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>4</v>
       </c>
       <c r="Y12" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z12">
         <v>11.5</v>
       </c>
       <c r="AA12" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB12">
         <v>3.8</v>
       </c>
       <c r="AC12" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD12">
         <v>4</v>
       </c>
       <c r="AE12" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF12">
         <v>4</v>
       </c>
       <c r="AG12" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH12">
         <v>4</v>
       </c>
       <c r="AI12" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ12">
         <v>4</v>
       </c>
       <c r="AK12" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL12">
         <v>4</v>
       </c>
       <c r="AM12" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AN12">
         <v>12</v>
       </c>
       <c r="AO12" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AP12">
         <v>4</v>
       </c>
       <c r="AQ12" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AR12">
         <v>4</v>
       </c>
       <c r="AS12" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AT12">
         <v>4</v>
       </c>
       <c r="AU12" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV12">
         <v>4</v>
       </c>
       <c r="AW12" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AX12">
         <v>4</v>
       </c>
       <c r="AY12" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AZ12">
         <v>4</v>
       </c>
       <c r="BA12" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BB12">
         <v>11.5</v>
       </c>
       <c r="BC12" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BD12">
         <v>3.8</v>
       </c>
       <c r="BE12" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF12">
         <v>4</v>
       </c>
       <c r="BG12" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH12">
         <v>4</v>
       </c>
       <c r="BI12" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BJ12">
         <v>4</v>
       </c>
       <c r="BK12" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BL12">
         <v>4</v>
       </c>
       <c r="BM12" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BN12">
         <v>4</v>
       </c>
       <c r="BO12" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BP12">
         <v>12</v>
@@ -1426,188 +1588,203 @@
       <c r="A13">
         <v>4</v>
       </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>44470</v>
+      </c>
+      <c r="E13" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13" t="s">
+        <v>3</v>
+      </c>
       <c r="G13" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>9.5</v>
       </c>
       <c r="M13" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>4</v>
       </c>
       <c r="O13" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P13">
         <v>4</v>
       </c>
       <c r="Q13" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R13">
         <v>4</v>
       </c>
       <c r="S13" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T13">
         <v>4</v>
       </c>
       <c r="U13" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>4</v>
       </c>
       <c r="W13" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>4</v>
       </c>
       <c r="Y13" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z13">
         <v>11.5</v>
       </c>
       <c r="AA13" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB13">
         <v>3.8</v>
       </c>
       <c r="AC13" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD13">
         <v>4</v>
       </c>
       <c r="AE13" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF13">
         <v>4</v>
       </c>
       <c r="AG13" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH13">
         <v>4</v>
       </c>
       <c r="AI13" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ13">
         <v>4</v>
       </c>
       <c r="AK13" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL13">
         <v>4</v>
       </c>
       <c r="AM13" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AN13">
         <v>12</v>
       </c>
       <c r="AO13" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AP13">
         <v>4</v>
       </c>
       <c r="AQ13" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AR13">
         <v>4</v>
       </c>
       <c r="AS13" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AT13">
         <v>4</v>
       </c>
       <c r="AU13" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV13">
         <v>4</v>
       </c>
       <c r="AW13" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AX13">
         <v>4</v>
       </c>
       <c r="AY13" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AZ13">
         <v>4</v>
       </c>
       <c r="BA13" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BB13">
         <v>11.5</v>
       </c>
       <c r="BC13" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BD13">
         <v>3.8</v>
       </c>
       <c r="BE13" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF13">
         <v>4</v>
       </c>
       <c r="BG13" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH13">
         <v>4</v>
       </c>
       <c r="BI13" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BJ13">
         <v>4</v>
       </c>
       <c r="BK13" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BL13">
         <v>4</v>
       </c>
       <c r="BM13" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BN13">
         <v>4</v>
       </c>
       <c r="BO13" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BP13">
         <v>12</v>
@@ -1617,188 +1794,203 @@
       <c r="A14">
         <v>5</v>
       </c>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>44470</v>
+      </c>
+      <c r="E14" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14" t="s">
+        <v>3</v>
+      </c>
       <c r="G14" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H14">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L14">
         <v>10.5</v>
       </c>
       <c r="M14" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>4</v>
       </c>
       <c r="O14" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P14">
         <v>4</v>
       </c>
       <c r="Q14" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R14">
         <v>4</v>
       </c>
       <c r="S14" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T14">
         <v>4</v>
       </c>
       <c r="U14" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>4</v>
       </c>
       <c r="W14" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>4</v>
       </c>
       <c r="Y14" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z14">
         <v>11.5</v>
       </c>
       <c r="AA14" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB14">
         <v>3.8</v>
       </c>
       <c r="AC14" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD14">
         <v>4</v>
       </c>
       <c r="AE14" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF14">
         <v>4</v>
       </c>
       <c r="AG14" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH14">
         <v>4</v>
       </c>
       <c r="AI14" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ14">
         <v>4</v>
       </c>
       <c r="AK14" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL14">
         <v>4</v>
       </c>
       <c r="AM14" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AN14">
         <v>12</v>
       </c>
       <c r="AO14" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AP14">
         <v>4</v>
       </c>
       <c r="AQ14" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AR14">
         <v>4</v>
       </c>
       <c r="AS14" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AT14">
         <v>4</v>
       </c>
       <c r="AU14" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV14">
         <v>4</v>
       </c>
       <c r="AW14" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AX14">
         <v>4</v>
       </c>
       <c r="AY14" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AZ14">
         <v>4</v>
       </c>
       <c r="BA14" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BB14">
         <v>11.5</v>
       </c>
       <c r="BC14" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BD14">
         <v>3.8</v>
       </c>
       <c r="BE14" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF14">
         <v>4</v>
       </c>
       <c r="BG14" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH14">
         <v>4</v>
       </c>
       <c r="BI14" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BJ14">
         <v>4</v>
       </c>
       <c r="BK14" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BL14">
         <v>4</v>
       </c>
       <c r="BM14" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BN14">
         <v>4</v>
       </c>
       <c r="BO14" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BP14">
         <v>12</v>
@@ -1808,14 +2000,29 @@
       <c r="A15">
         <v>6</v>
       </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>44470</v>
+      </c>
+      <c r="E15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15" t="s">
+        <v>3</v>
+      </c>
       <c r="G15" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H15">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1824,37 +2031,37 @@
         <v>0</v>
       </c>
       <c r="M15" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>4</v>
       </c>
       <c r="O15" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P15">
         <v>4</v>
       </c>
       <c r="Q15" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R15">
         <v>4</v>
       </c>
       <c r="S15" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T15">
         <v>4</v>
       </c>
       <c r="U15" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>4</v>
       </c>
       <c r="W15" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>4</v>
@@ -1863,37 +2070,37 @@
         <v>0</v>
       </c>
       <c r="AA15" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB15">
         <v>4</v>
       </c>
       <c r="AC15" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD15">
         <v>4</v>
       </c>
       <c r="AE15" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF15">
         <v>4</v>
       </c>
       <c r="AG15" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH15">
         <v>4</v>
       </c>
       <c r="AI15" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ15">
         <v>4</v>
       </c>
       <c r="AK15" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL15">
         <v>4</v>
@@ -1902,37 +2109,37 @@
         <v>0</v>
       </c>
       <c r="AO15" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AP15">
         <v>4</v>
       </c>
       <c r="AQ15" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AR15">
         <v>4</v>
       </c>
       <c r="AS15" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AT15">
         <v>4</v>
       </c>
       <c r="AU15" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV15">
         <v>4</v>
       </c>
       <c r="AW15" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AX15">
         <v>4</v>
       </c>
       <c r="AY15" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AZ15">
         <v>4</v>
@@ -1941,37 +2148,37 @@
         <v>0</v>
       </c>
       <c r="BC15" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BD15">
         <v>4</v>
       </c>
       <c r="BE15" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF15">
         <v>4</v>
       </c>
       <c r="BG15" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH15">
         <v>4</v>
       </c>
       <c r="BI15" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BJ15">
         <v>4</v>
       </c>
       <c r="BK15" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BL15">
         <v>4</v>
       </c>
       <c r="BM15" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BN15">
         <v>4</v>
@@ -1984,14 +2191,29 @@
       <c r="A16">
         <v>7</v>
       </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>44470</v>
+      </c>
+      <c r="E16" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" t="s">
+        <v>3</v>
+      </c>
       <c r="G16" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H16">
         <v>4</v>
       </c>
       <c r="I16" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J16">
         <v>4</v>
@@ -2000,37 +2222,37 @@
         <v>0</v>
       </c>
       <c r="M16" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>4</v>
       </c>
       <c r="O16" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P16">
         <v>4</v>
       </c>
       <c r="Q16" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R16">
         <v>4</v>
       </c>
       <c r="S16" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T16">
         <v>4</v>
       </c>
       <c r="U16" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>4</v>
       </c>
       <c r="W16" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>4</v>
@@ -2039,37 +2261,37 @@
         <v>0</v>
       </c>
       <c r="AA16" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB16">
         <v>4</v>
       </c>
       <c r="AC16" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD16">
         <v>4</v>
       </c>
       <c r="AE16" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF16">
         <v>4</v>
       </c>
       <c r="AG16" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH16">
         <v>4</v>
       </c>
       <c r="AI16" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ16">
         <v>4</v>
       </c>
       <c r="AK16" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL16">
         <v>4</v>
@@ -2078,37 +2300,37 @@
         <v>0</v>
       </c>
       <c r="AO16" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AP16">
         <v>4</v>
       </c>
       <c r="AQ16" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AR16">
         <v>4</v>
       </c>
       <c r="AS16" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AT16">
         <v>4</v>
       </c>
       <c r="AU16" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV16">
         <v>4</v>
       </c>
       <c r="AW16" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AX16">
         <v>4</v>
       </c>
       <c r="AY16" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AZ16">
         <v>4</v>
@@ -2117,37 +2339,37 @@
         <v>0</v>
       </c>
       <c r="BC16" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BD16">
         <v>4</v>
       </c>
       <c r="BE16" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF16">
         <v>4</v>
       </c>
       <c r="BG16" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH16">
         <v>4</v>
       </c>
       <c r="BI16" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BJ16">
         <v>4</v>
       </c>
       <c r="BK16" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BL16">
         <v>4</v>
       </c>
       <c r="BM16" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BN16">
         <v>4</v>
@@ -2160,14 +2382,29 @@
       <c r="A17">
         <v>8</v>
       </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>44470</v>
+      </c>
+      <c r="E17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F17" t="s">
+        <v>3</v>
+      </c>
       <c r="G17" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H17">
         <v>4</v>
       </c>
       <c r="I17" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J17">
         <v>4</v>
@@ -2176,37 +2413,37 @@
         <v>0</v>
       </c>
       <c r="M17" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>4</v>
       </c>
       <c r="O17" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P17">
         <v>4</v>
       </c>
       <c r="Q17" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R17">
         <v>4</v>
       </c>
       <c r="S17" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T17">
         <v>4</v>
       </c>
       <c r="U17" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>4</v>
       </c>
       <c r="W17" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>4</v>
@@ -2215,37 +2452,37 @@
         <v>0</v>
       </c>
       <c r="AA17" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB17">
         <v>4</v>
       </c>
       <c r="AC17" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD17">
         <v>4</v>
       </c>
       <c r="AE17" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF17">
         <v>4</v>
       </c>
       <c r="AG17" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH17">
         <v>4</v>
       </c>
       <c r="AI17" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ17">
         <v>4</v>
       </c>
       <c r="AK17" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL17">
         <v>4</v>
@@ -2254,37 +2491,37 @@
         <v>0</v>
       </c>
       <c r="AO17" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AP17">
         <v>4</v>
       </c>
       <c r="AQ17" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AR17">
         <v>4</v>
       </c>
       <c r="AS17" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AT17">
         <v>4</v>
       </c>
       <c r="AU17" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV17">
         <v>4</v>
       </c>
       <c r="AW17" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AX17">
         <v>4</v>
       </c>
       <c r="AY17" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AZ17">
         <v>4</v>
@@ -2293,37 +2530,37 @@
         <v>0</v>
       </c>
       <c r="BC17" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BD17">
         <v>4</v>
       </c>
       <c r="BE17" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF17">
         <v>4</v>
       </c>
       <c r="BG17" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH17">
         <v>4</v>
       </c>
       <c r="BI17" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BJ17">
         <v>4</v>
       </c>
       <c r="BK17" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BL17">
         <v>4</v>
       </c>
       <c r="BM17" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BN17">
         <v>4</v>
@@ -2336,14 +2573,29 @@
       <c r="A18">
         <v>9</v>
       </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>44470</v>
+      </c>
+      <c r="E18" t="s">
+        <v>2</v>
+      </c>
+      <c r="F18" t="s">
+        <v>3</v>
+      </c>
       <c r="G18" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H18">
         <v>4</v>
       </c>
       <c r="I18" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J18">
         <v>4</v>
@@ -2352,37 +2604,37 @@
         <v>0</v>
       </c>
       <c r="M18" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>4</v>
       </c>
       <c r="O18" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P18">
         <v>4</v>
       </c>
       <c r="Q18" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R18">
         <v>4</v>
       </c>
       <c r="S18" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="T18">
         <v>4</v>
       </c>
       <c r="U18" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>4</v>
       </c>
       <c r="W18" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>4</v>
@@ -2391,37 +2643,37 @@
         <v>0</v>
       </c>
       <c r="AA18" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB18">
         <v>4</v>
       </c>
       <c r="AC18" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD18">
         <v>4</v>
       </c>
       <c r="AE18" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AF18">
         <v>4</v>
       </c>
       <c r="AG18" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH18">
         <v>4</v>
       </c>
       <c r="AI18" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ18">
         <v>4</v>
       </c>
       <c r="AK18" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL18">
         <v>4</v>
@@ -2430,37 +2682,37 @@
         <v>0</v>
       </c>
       <c r="AO18" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AP18">
         <v>4</v>
       </c>
       <c r="AQ18" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AR18">
         <v>4</v>
       </c>
       <c r="AS18" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AT18">
         <v>4</v>
       </c>
       <c r="AU18" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV18">
         <v>4</v>
       </c>
       <c r="AW18" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AX18">
         <v>4</v>
       </c>
       <c r="AY18" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AZ18">
         <v>4</v>
@@ -2469,37 +2721,37 @@
         <v>0</v>
       </c>
       <c r="BC18" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BD18">
         <v>4</v>
       </c>
       <c r="BE18" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BF18">
         <v>4</v>
       </c>
       <c r="BG18" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH18">
         <v>4</v>
       </c>
       <c r="BI18" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BJ18">
         <v>4</v>
       </c>
       <c r="BK18" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BL18">
         <v>4</v>
       </c>
       <c r="BM18" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BN18">
         <v>4</v>
@@ -2510,190 +2762,205 @@
     </row>
     <row r="19" spans="1:68">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19">
+        <v>44470</v>
+      </c>
+      <c r="E19" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19" t="s">
+        <v>23</v>
       </c>
       <c r="G19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="N19">
         <v>0</v>
       </c>
       <c r="O19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="P19">
         <v>0</v>
       </c>
       <c r="Q19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="R19">
         <v>0</v>
       </c>
       <c r="S19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="T19">
         <v>0</v>
       </c>
       <c r="U19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="V19">
         <v>0</v>
       </c>
       <c r="W19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="X19">
         <v>0</v>
       </c>
       <c r="Y19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="Z19">
         <v>0</v>
       </c>
       <c r="AA19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AB19">
         <v>0</v>
       </c>
       <c r="AC19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AD19">
         <v>0</v>
       </c>
       <c r="AE19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AF19">
         <v>0</v>
       </c>
       <c r="AG19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AI19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AJ19">
         <v>0</v>
       </c>
       <c r="AK19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AN19">
         <v>0</v>
       </c>
       <c r="AO19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AP19">
         <v>0</v>
       </c>
       <c r="AQ19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AR19">
         <v>0</v>
       </c>
       <c r="AS19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AT19">
         <v>0</v>
       </c>
       <c r="AU19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AV19">
         <v>0</v>
       </c>
       <c r="AW19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AX19">
         <v>0</v>
       </c>
       <c r="AY19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AZ19">
         <v>0</v>
       </c>
       <c r="BA19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BB19">
         <v>0</v>
       </c>
       <c r="BC19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BD19">
         <v>0</v>
       </c>
       <c r="BE19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BF19">
         <v>0</v>
       </c>
       <c r="BG19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BH19">
         <v>0</v>
       </c>
       <c r="BI19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BJ19">
         <v>0</v>
       </c>
       <c r="BK19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BL19">
         <v>0</v>
       </c>
       <c r="BM19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BN19">
         <v>0</v>
       </c>
       <c r="BO19" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BP19">
         <v>0</v>
@@ -2701,190 +2968,205 @@
     </row>
     <row r="20" spans="1:68">
       <c r="A20" t="s">
-        <v>7</v>
+        <v>25</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20">
+        <v>44470</v>
+      </c>
+      <c r="E20" t="s">
+        <v>2</v>
+      </c>
+      <c r="F20" t="s">
+        <v>23</v>
       </c>
       <c r="G20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="N20">
         <v>0</v>
       </c>
       <c r="O20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="P20">
         <v>0</v>
       </c>
       <c r="Q20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="R20">
         <v>0</v>
       </c>
       <c r="S20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="T20">
         <v>0</v>
       </c>
       <c r="U20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="V20">
         <v>0</v>
       </c>
       <c r="W20" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="X20">
         <v>0</v>
       </c>
       <c r="Y20" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="Z20">
         <v>0</v>
       </c>
       <c r="AA20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AB20">
         <v>0</v>
       </c>
       <c r="AC20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AD20">
         <v>0</v>
       </c>
       <c r="AE20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AF20">
         <v>0</v>
       </c>
       <c r="AG20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AI20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AJ20">
         <v>0</v>
       </c>
       <c r="AK20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AN20">
         <v>0</v>
       </c>
       <c r="AO20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AP20">
         <v>0</v>
       </c>
       <c r="AQ20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AR20">
         <v>0</v>
       </c>
       <c r="AS20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AT20">
         <v>0</v>
       </c>
       <c r="AU20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AV20">
         <v>0</v>
       </c>
       <c r="AW20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AX20">
         <v>0</v>
       </c>
       <c r="AY20" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AZ20">
         <v>0</v>
       </c>
       <c r="BA20" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BB20">
         <v>0</v>
       </c>
       <c r="BC20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BD20">
         <v>0</v>
       </c>
       <c r="BE20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BF20">
         <v>0</v>
       </c>
       <c r="BG20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BH20">
         <v>0</v>
       </c>
       <c r="BI20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BJ20">
         <v>0</v>
       </c>
       <c r="BK20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BL20">
         <v>0</v>
       </c>
       <c r="BM20" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BN20">
         <v>0</v>
       </c>
       <c r="BO20" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BP20">
         <v>0</v>
@@ -2892,190 +3174,205 @@
     </row>
     <row r="21" spans="1:68">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>28</v>
+      </c>
+      <c r="B21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21">
+        <v>44470</v>
+      </c>
+      <c r="E21" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" t="s">
+        <v>23</v>
       </c>
       <c r="G21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="N21">
         <v>0</v>
       </c>
       <c r="O21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="P21">
         <v>0</v>
       </c>
       <c r="Q21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="R21">
         <v>0</v>
       </c>
       <c r="S21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="T21">
         <v>0</v>
       </c>
       <c r="U21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="V21">
         <v>0</v>
       </c>
       <c r="W21" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="X21">
         <v>0</v>
       </c>
       <c r="Y21" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="Z21">
         <v>0</v>
       </c>
       <c r="AA21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AB21">
         <v>0</v>
       </c>
       <c r="AC21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AD21">
         <v>0</v>
       </c>
       <c r="AE21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AF21">
         <v>0</v>
       </c>
       <c r="AG21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AI21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AJ21">
         <v>0</v>
       </c>
       <c r="AK21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AN21">
         <v>0</v>
       </c>
       <c r="AO21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AP21">
         <v>0</v>
       </c>
       <c r="AQ21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AR21">
         <v>0</v>
       </c>
       <c r="AS21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AT21">
         <v>0</v>
       </c>
       <c r="AU21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AV21">
         <v>0</v>
       </c>
       <c r="AW21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AX21">
         <v>0</v>
       </c>
       <c r="AY21" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AZ21">
         <v>0</v>
       </c>
       <c r="BA21" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BB21">
         <v>0</v>
       </c>
       <c r="BC21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BD21">
         <v>0</v>
       </c>
       <c r="BE21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BF21">
         <v>0</v>
       </c>
       <c r="BG21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BH21">
         <v>0</v>
       </c>
       <c r="BI21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BJ21">
         <v>0</v>
       </c>
       <c r="BK21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BL21">
         <v>0</v>
       </c>
       <c r="BM21" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BN21">
         <v>0</v>
       </c>
       <c r="BO21" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BP21">
         <v>0</v>
@@ -3083,190 +3380,205 @@
     </row>
     <row r="22" spans="1:68">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>31</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22">
+        <v>44470</v>
+      </c>
+      <c r="E22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F22" t="s">
+        <v>23</v>
       </c>
       <c r="G22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="N22">
         <v>0</v>
       </c>
       <c r="O22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="P22">
         <v>0</v>
       </c>
       <c r="Q22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="R22">
         <v>0</v>
       </c>
       <c r="S22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="T22">
         <v>0</v>
       </c>
       <c r="U22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="V22">
         <v>0</v>
       </c>
       <c r="W22" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="X22">
         <v>0</v>
       </c>
       <c r="Y22" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="Z22">
         <v>0</v>
       </c>
       <c r="AA22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AB22">
         <v>0</v>
       </c>
       <c r="AC22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AD22">
         <v>0</v>
       </c>
       <c r="AE22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AF22">
         <v>0</v>
       </c>
       <c r="AG22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AI22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AJ22">
         <v>0</v>
       </c>
       <c r="AK22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AL22">
         <v>0</v>
       </c>
       <c r="AM22" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AN22">
         <v>0</v>
       </c>
       <c r="AO22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AP22">
         <v>0</v>
       </c>
       <c r="AQ22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AR22">
         <v>0</v>
       </c>
       <c r="AS22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AT22">
         <v>0</v>
       </c>
       <c r="AU22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AV22">
         <v>0</v>
       </c>
       <c r="AW22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AX22">
         <v>0</v>
       </c>
       <c r="AY22" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AZ22">
         <v>0</v>
       </c>
       <c r="BA22" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BB22">
         <v>0</v>
       </c>
       <c r="BC22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BD22">
         <v>0</v>
       </c>
       <c r="BE22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BF22">
         <v>0</v>
       </c>
       <c r="BG22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BH22">
         <v>0</v>
       </c>
       <c r="BI22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BJ22">
         <v>0</v>
       </c>
       <c r="BK22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BL22">
         <v>0</v>
       </c>
       <c r="BM22" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BN22">
         <v>0</v>
       </c>
       <c r="BO22" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BP22">
         <v>0</v>
@@ -3274,190 +3586,205 @@
     </row>
     <row r="23" spans="1:68">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>33</v>
+      </c>
+      <c r="B23" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23">
+        <v>44470</v>
+      </c>
+      <c r="E23" t="s">
+        <v>2</v>
+      </c>
+      <c r="F23" t="s">
+        <v>23</v>
       </c>
       <c r="G23" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="N23">
         <v>0</v>
       </c>
       <c r="O23" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="P23">
         <v>0</v>
       </c>
       <c r="Q23" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="R23">
         <v>0</v>
       </c>
       <c r="S23" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="T23">
         <v>0</v>
       </c>
       <c r="U23" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="V23">
         <v>0</v>
       </c>
       <c r="W23" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="X23">
         <v>0</v>
       </c>
       <c r="Y23" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="Z23">
         <v>0</v>
       </c>
       <c r="AA23" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AB23">
         <v>0</v>
       </c>
       <c r="AC23" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AD23">
         <v>0</v>
       </c>
       <c r="AE23" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AF23">
         <v>0</v>
       </c>
       <c r="AG23" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AI23" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AJ23">
         <v>0</v>
       </c>
       <c r="AK23" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AL23">
         <v>0</v>
       </c>
       <c r="AM23" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AN23">
         <v>0</v>
       </c>
       <c r="AO23" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AP23">
         <v>0</v>
       </c>
       <c r="AQ23" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AR23">
         <v>0</v>
       </c>
       <c r="AS23" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AT23">
         <v>0</v>
       </c>
       <c r="AU23" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AV23">
         <v>0</v>
       </c>
       <c r="AW23" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AX23">
         <v>0</v>
       </c>
       <c r="AY23" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AZ23">
         <v>0</v>
       </c>
       <c r="BA23" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BB23">
         <v>0</v>
       </c>
       <c r="BC23" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BD23">
         <v>0</v>
       </c>
       <c r="BE23" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BF23">
         <v>0</v>
       </c>
       <c r="BG23" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BH23">
         <v>0</v>
       </c>
       <c r="BI23" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BJ23">
         <v>0</v>
       </c>
       <c r="BK23" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BL23">
         <v>0</v>
       </c>
       <c r="BM23" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BN23">
         <v>0</v>
       </c>
       <c r="BO23" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BP23">
         <v>0</v>
@@ -3465,190 +3792,205 @@
     </row>
     <row r="24" spans="1:68">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>35</v>
+      </c>
+      <c r="B24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24">
+        <v>44470</v>
+      </c>
+      <c r="E24" t="s">
+        <v>2</v>
+      </c>
+      <c r="F24" t="s">
+        <v>23</v>
       </c>
       <c r="G24" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="N24">
         <v>0</v>
       </c>
       <c r="O24" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="P24">
         <v>0</v>
       </c>
       <c r="Q24" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="R24">
         <v>0</v>
       </c>
       <c r="S24" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="T24">
         <v>0</v>
       </c>
       <c r="U24" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="V24">
         <v>0</v>
       </c>
       <c r="W24" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="X24">
         <v>0</v>
       </c>
       <c r="Y24" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="Z24">
         <v>0</v>
       </c>
       <c r="AA24" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AB24">
         <v>0</v>
       </c>
       <c r="AC24" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AD24">
         <v>0</v>
       </c>
       <c r="AE24" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AF24">
         <v>0</v>
       </c>
       <c r="AG24" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AI24" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AJ24">
         <v>0</v>
       </c>
       <c r="AK24" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AL24">
         <v>0</v>
       </c>
       <c r="AM24" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AN24">
         <v>0</v>
       </c>
       <c r="AO24" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AP24">
         <v>0</v>
       </c>
       <c r="AQ24" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AR24">
         <v>0</v>
       </c>
       <c r="AS24" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AT24">
         <v>0</v>
       </c>
       <c r="AU24" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AV24">
         <v>0</v>
       </c>
       <c r="AW24" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AX24">
         <v>0</v>
       </c>
       <c r="AY24" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AZ24">
         <v>0</v>
       </c>
       <c r="BA24" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BB24">
         <v>0</v>
       </c>
       <c r="BC24" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BD24">
         <v>0</v>
       </c>
       <c r="BE24" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BF24">
         <v>0</v>
       </c>
       <c r="BG24" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BH24">
         <v>0</v>
       </c>
       <c r="BI24" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BJ24">
         <v>0</v>
       </c>
       <c r="BK24" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BL24">
         <v>0</v>
       </c>
       <c r="BM24" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BN24">
         <v>0</v>
       </c>
       <c r="BO24" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BP24">
         <v>0</v>
@@ -3656,190 +3998,205 @@
     </row>
     <row r="25" spans="1:68">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>37</v>
+      </c>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25">
+        <v>44470</v>
+      </c>
+      <c r="E25" t="s">
+        <v>2</v>
+      </c>
+      <c r="F25" t="s">
+        <v>23</v>
       </c>
       <c r="G25" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="H25">
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="N25">
         <v>0</v>
       </c>
       <c r="O25" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="P25">
         <v>0</v>
       </c>
       <c r="Q25" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="R25">
         <v>0</v>
       </c>
       <c r="S25" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="T25">
         <v>0</v>
       </c>
       <c r="U25" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="V25">
         <v>0</v>
       </c>
       <c r="W25" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="X25">
         <v>0</v>
       </c>
       <c r="Y25" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="Z25">
         <v>0</v>
       </c>
       <c r="AA25" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AB25">
         <v>0</v>
       </c>
       <c r="AC25" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AD25">
         <v>0</v>
       </c>
       <c r="AE25" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AF25">
         <v>0</v>
       </c>
       <c r="AG25" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AH25">
         <v>0</v>
       </c>
       <c r="AI25" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AJ25">
         <v>0</v>
       </c>
       <c r="AK25" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AL25">
         <v>0</v>
       </c>
       <c r="AM25" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AN25">
         <v>0</v>
       </c>
       <c r="AO25" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AP25">
         <v>0</v>
       </c>
       <c r="AQ25" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AR25">
         <v>0</v>
       </c>
       <c r="AS25" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AT25">
         <v>0</v>
       </c>
       <c r="AU25" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AV25">
         <v>0</v>
       </c>
       <c r="AW25" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AX25">
         <v>0</v>
       </c>
       <c r="AY25" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AZ25">
         <v>0</v>
       </c>
       <c r="BA25" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BB25">
         <v>0</v>
       </c>
       <c r="BC25" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BD25">
         <v>0</v>
       </c>
       <c r="BE25" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BF25">
         <v>0</v>
       </c>
       <c r="BG25" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BH25">
         <v>0</v>
       </c>
       <c r="BI25" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BJ25">
         <v>0</v>
       </c>
       <c r="BK25" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BL25">
         <v>0</v>
       </c>
       <c r="BM25" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BN25">
         <v>0</v>
       </c>
       <c r="BO25" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BP25">
         <v>0</v>
@@ -3847,190 +4204,205 @@
     </row>
     <row r="26" spans="1:68">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>39</v>
+      </c>
+      <c r="B26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26">
+        <v>44470</v>
+      </c>
+      <c r="E26" t="s">
+        <v>2</v>
+      </c>
+      <c r="F26" t="s">
+        <v>23</v>
       </c>
       <c r="G26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="H26">
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L26">
         <v>0</v>
       </c>
       <c r="M26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="N26">
         <v>0</v>
       </c>
       <c r="O26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="P26">
         <v>0</v>
       </c>
       <c r="Q26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="R26">
         <v>0</v>
       </c>
       <c r="S26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="T26">
         <v>0</v>
       </c>
       <c r="U26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="V26">
         <v>0</v>
       </c>
       <c r="W26" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="X26">
         <v>0</v>
       </c>
       <c r="Y26" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="Z26">
         <v>0</v>
       </c>
       <c r="AA26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AB26">
         <v>0</v>
       </c>
       <c r="AC26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AD26">
         <v>0</v>
       </c>
       <c r="AE26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AF26">
         <v>0</v>
       </c>
       <c r="AG26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AI26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AJ26">
         <v>0</v>
       </c>
       <c r="AK26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AL26">
         <v>0</v>
       </c>
       <c r="AM26" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AN26">
         <v>0</v>
       </c>
       <c r="AO26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AP26">
         <v>0</v>
       </c>
       <c r="AQ26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AR26">
         <v>0</v>
       </c>
       <c r="AS26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AT26">
         <v>0</v>
       </c>
       <c r="AU26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AV26">
         <v>0</v>
       </c>
       <c r="AW26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AX26">
         <v>0</v>
       </c>
       <c r="AY26" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AZ26">
         <v>0</v>
       </c>
       <c r="BA26" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BB26">
         <v>0</v>
       </c>
       <c r="BC26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BD26">
         <v>0</v>
       </c>
       <c r="BE26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BF26">
         <v>0</v>
       </c>
       <c r="BG26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BH26">
         <v>0</v>
       </c>
       <c r="BI26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BJ26">
         <v>0</v>
       </c>
       <c r="BK26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BL26">
         <v>0</v>
       </c>
       <c r="BM26" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BN26">
         <v>0</v>
       </c>
       <c r="BO26" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BP26">
         <v>0</v>
@@ -4038,190 +4410,205 @@
     </row>
     <row r="27" spans="1:68">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>41</v>
+      </c>
+      <c r="B27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27">
+        <v>44470</v>
+      </c>
+      <c r="E27" t="s">
+        <v>2</v>
+      </c>
+      <c r="F27" t="s">
+        <v>23</v>
       </c>
       <c r="G27" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="H27">
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="N27">
         <v>0</v>
       </c>
       <c r="O27" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="P27">
         <v>0</v>
       </c>
       <c r="Q27" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="R27">
         <v>0</v>
       </c>
       <c r="S27" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="T27">
         <v>0</v>
       </c>
       <c r="U27" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="V27">
         <v>0</v>
       </c>
       <c r="W27" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="X27">
         <v>0</v>
       </c>
       <c r="Y27" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="Z27">
         <v>0</v>
       </c>
       <c r="AA27" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AB27">
         <v>0</v>
       </c>
       <c r="AC27" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AD27">
         <v>0</v>
       </c>
       <c r="AE27" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AF27">
         <v>0</v>
       </c>
       <c r="AG27" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AI27" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AJ27">
         <v>0</v>
       </c>
       <c r="AK27" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AL27">
         <v>0</v>
       </c>
       <c r="AM27" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AN27">
         <v>0</v>
       </c>
       <c r="AO27" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AP27">
         <v>0</v>
       </c>
       <c r="AQ27" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AR27">
         <v>0</v>
       </c>
       <c r="AS27" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AT27">
         <v>0</v>
       </c>
       <c r="AU27" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AV27">
         <v>0</v>
       </c>
       <c r="AW27" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AX27">
         <v>0</v>
       </c>
       <c r="AY27" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AZ27">
         <v>0</v>
       </c>
       <c r="BA27" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BB27">
         <v>0</v>
       </c>
       <c r="BC27" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BD27">
         <v>0</v>
       </c>
       <c r="BE27" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BF27">
         <v>0</v>
       </c>
       <c r="BG27" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BH27">
         <v>0</v>
       </c>
       <c r="BI27" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BJ27">
         <v>0</v>
       </c>
       <c r="BK27" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BL27">
         <v>0</v>
       </c>
       <c r="BM27" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BN27">
         <v>0</v>
       </c>
       <c r="BO27" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BP27">
         <v>0</v>
@@ -4229,190 +4616,205 @@
     </row>
     <row r="28" spans="1:68">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>43</v>
+      </c>
+      <c r="B28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28">
+        <v>44470</v>
+      </c>
+      <c r="E28" t="s">
+        <v>2</v>
+      </c>
+      <c r="F28" t="s">
+        <v>23</v>
       </c>
       <c r="G28" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="H28">
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L28">
         <v>0</v>
       </c>
       <c r="M28" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="N28">
         <v>0</v>
       </c>
       <c r="O28" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="P28">
         <v>0</v>
       </c>
       <c r="Q28" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="R28">
         <v>0</v>
       </c>
       <c r="S28" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="T28">
         <v>0</v>
       </c>
       <c r="U28" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="V28">
         <v>0</v>
       </c>
       <c r="W28" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="X28">
         <v>0</v>
       </c>
       <c r="Y28" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="Z28">
         <v>0</v>
       </c>
       <c r="AA28" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AB28">
         <v>0</v>
       </c>
       <c r="AC28" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AD28">
         <v>0</v>
       </c>
       <c r="AE28" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AF28">
         <v>0</v>
       </c>
       <c r="AG28" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AI28" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AJ28">
         <v>0</v>
       </c>
       <c r="AK28" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AL28">
         <v>0</v>
       </c>
       <c r="AM28" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AN28">
         <v>0</v>
       </c>
       <c r="AO28" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AP28">
         <v>0</v>
       </c>
       <c r="AQ28" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AR28">
         <v>0</v>
       </c>
       <c r="AS28" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AT28">
         <v>0</v>
       </c>
       <c r="AU28" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AV28">
         <v>0</v>
       </c>
       <c r="AW28" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AX28">
         <v>0</v>
       </c>
       <c r="AY28" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AZ28">
         <v>0</v>
       </c>
       <c r="BA28" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BB28">
         <v>0</v>
       </c>
       <c r="BC28" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BD28">
         <v>0</v>
       </c>
       <c r="BE28" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BF28">
         <v>0</v>
       </c>
       <c r="BG28" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BH28">
         <v>0</v>
       </c>
       <c r="BI28" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BJ28">
         <v>0</v>
       </c>
       <c r="BK28" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BL28">
         <v>0</v>
       </c>
       <c r="BM28" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BN28">
         <v>0</v>
       </c>
       <c r="BO28" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BP28">
         <v>0</v>
@@ -4420,184 +4822,199 @@
     </row>
     <row r="29" spans="1:68">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>45</v>
+      </c>
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29">
+        <v>44470</v>
+      </c>
+      <c r="E29" t="s">
+        <v>2</v>
+      </c>
+      <c r="F29" t="s">
+        <v>23</v>
       </c>
       <c r="G29" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="H29">
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L29">
         <v>0</v>
       </c>
       <c r="M29" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="N29">
         <v>0</v>
       </c>
       <c r="O29" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="P29">
         <v>0</v>
       </c>
       <c r="Q29" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="R29">
         <v>0</v>
       </c>
       <c r="S29" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="T29">
         <v>0</v>
       </c>
       <c r="U29" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="V29">
         <v>0</v>
       </c>
       <c r="W29" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="X29">
         <v>0</v>
       </c>
       <c r="Y29" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="Z29">
         <v>0</v>
       </c>
       <c r="AA29" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AB29">
         <v>0</v>
       </c>
       <c r="AC29" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AD29">
         <v>0</v>
       </c>
       <c r="AE29" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AF29">
         <v>0</v>
       </c>
       <c r="AG29" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AH29">
         <v>0</v>
       </c>
       <c r="AI29" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AJ29">
         <v>0</v>
       </c>
       <c r="AK29" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AL29">
         <v>0</v>
       </c>
       <c r="AM29" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AN29">
         <v>0</v>
       </c>
       <c r="AO29" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AP29">
         <v>0</v>
       </c>
       <c r="AQ29" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AR29">
         <v>0</v>
       </c>
       <c r="AS29" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AT29">
         <v>0</v>
       </c>
       <c r="AU29" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AV29">
         <v>0</v>
       </c>
       <c r="AW29" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="AX29">
         <v>0</v>
       </c>
       <c r="AY29" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AZ29">
         <v>0</v>
       </c>
       <c r="BA29" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="BB29">
         <v>0</v>
       </c>
       <c r="BC29" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BD29">
         <v>0</v>
       </c>
       <c r="BE29" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BF29">
         <v>0</v>
       </c>
       <c r="BG29" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BH29">
         <v>0</v>
       </c>
       <c r="BI29" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BJ29">
         <v>0</v>
       </c>
       <c r="BK29" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BL29">
         <v>0</v>
       </c>
       <c r="BM29" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BN29">
         <v>0</v>

--- a/baocao1.xlsx
+++ b/baocao1.xlsx
@@ -625,7 +625,7 @@
         <v>37</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M8" t="s">
         <v>36</v>
@@ -667,7 +667,7 @@
         <v>37</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA8" t="s">
         <v>36</v>
@@ -709,7 +709,7 @@
         <v>37</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AO8" t="s">
         <v>36</v>
@@ -790,7 +790,7 @@
         <v>37</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:68">
@@ -906,7 +906,7 @@
         <v>37</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO9" t="s">
         <v>42</v>
@@ -987,7 +987,7 @@
         <v>37</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:68">
@@ -1025,7 +1025,7 @@
         <v>37</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="M10" t="s">
         <v>48</v>
@@ -1067,7 +1067,7 @@
         <v>37</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AA10" t="s">
         <v>47</v>
@@ -1109,7 +1109,7 @@
         <v>37</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AO10" t="s">
         <v>47</v>
@@ -1151,7 +1151,7 @@
         <v>37</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="BC10" t="s">
         <v>48</v>
